--- a/App_Inmuebles_Automatico/Cuota2026.xlsx
+++ b/App_Inmuebles_Automatico/Cuota2026.xlsx
@@ -10638,7 +10638,7 @@
         <v>101</v>
       </c>
       <c r="D2" s="9">
-        <v>1101</v>
+        <v>101</v>
       </c>
       <c r="E2" s="10">
         <v>163000</v>
@@ -10667,7 +10667,7 @@
         <v>102</v>
       </c>
       <c r="D3" s="9">
-        <v>1102</v>
+        <v>102</v>
       </c>
       <c r="E3" s="10">
         <v>152000</v>
@@ -10696,7 +10696,7 @@
         <v>106</v>
       </c>
       <c r="D4" s="9">
-        <v>1106</v>
+        <v>106</v>
       </c>
       <c r="E4" s="10">
         <v>163000</v>
@@ -10725,7 +10725,7 @@
         <v>107</v>
       </c>
       <c r="D5" s="9">
-        <v>1107</v>
+        <v>107</v>
       </c>
       <c r="E5" s="10">
         <v>163000</v>
@@ -10754,7 +10754,7 @@
         <v>108</v>
       </c>
       <c r="D6" s="9">
-        <v>1108</v>
+        <v>108</v>
       </c>
       <c r="E6" s="10">
         <v>152000</v>
@@ -10783,7 +10783,7 @@
         <v>201</v>
       </c>
       <c r="D7" s="9">
-        <v>1201</v>
+        <v>201</v>
       </c>
       <c r="E7" s="10">
         <v>163000</v>
@@ -10812,7 +10812,7 @@
         <v>202</v>
       </c>
       <c r="D8" s="9">
-        <v>1202</v>
+        <v>202</v>
       </c>
       <c r="E8" s="10">
         <v>163000</v>
@@ -10841,7 +10841,7 @@
         <v>203</v>
       </c>
       <c r="D9" s="9">
-        <v>1203</v>
+        <v>203</v>
       </c>
       <c r="E9" s="10">
         <v>152000</v>
@@ -10870,7 +10870,7 @@
         <v>204</v>
       </c>
       <c r="D10" s="9">
-        <v>1204</v>
+        <v>204</v>
       </c>
       <c r="E10" s="10">
         <v>163000</v>
@@ -10899,7 +10899,7 @@
         <v>205</v>
       </c>
       <c r="D11" s="9">
-        <v>1205</v>
+        <v>205</v>
       </c>
       <c r="E11" s="10">
         <v>163000</v>
@@ -10928,7 +10928,7 @@
         <v>206</v>
       </c>
       <c r="D12" s="9">
-        <v>1206</v>
+        <v>206</v>
       </c>
       <c r="E12" s="10">
         <v>163000</v>
@@ -10957,7 +10957,7 @@
         <v>207</v>
       </c>
       <c r="D13" s="9">
-        <v>1207</v>
+        <v>207</v>
       </c>
       <c r="E13" s="10">
         <v>163000</v>
@@ -10986,7 +10986,7 @@
         <v>208</v>
       </c>
       <c r="D14" s="9">
-        <v>1208</v>
+        <v>208</v>
       </c>
       <c r="E14" s="10">
         <v>163000</v>
@@ -11015,7 +11015,7 @@
         <v>301</v>
       </c>
       <c r="D15" s="9">
-        <v>1301</v>
+        <v>301</v>
       </c>
       <c r="E15" s="10">
         <v>163000</v>
@@ -11044,7 +11044,7 @@
         <v>302</v>
       </c>
       <c r="D16" s="9">
-        <v>1302</v>
+        <v>302</v>
       </c>
       <c r="E16" s="10">
         <v>163000</v>
@@ -11073,7 +11073,7 @@
         <v>303</v>
       </c>
       <c r="D17" s="9">
-        <v>1303</v>
+        <v>303</v>
       </c>
       <c r="E17" s="10">
         <v>163000</v>
@@ -11102,7 +11102,7 @@
         <v>304</v>
       </c>
       <c r="D18" s="9">
-        <v>1304</v>
+        <v>304</v>
       </c>
       <c r="E18" s="10">
         <v>163000</v>
@@ -11131,7 +11131,7 @@
         <v>305</v>
       </c>
       <c r="D19" s="9">
-        <v>1305</v>
+        <v>305</v>
       </c>
       <c r="E19" s="10">
         <v>163000</v>
@@ -11160,7 +11160,7 @@
         <v>306</v>
       </c>
       <c r="D20" s="9">
-        <v>1306</v>
+        <v>306</v>
       </c>
       <c r="E20" s="10">
         <v>163000</v>
@@ -11189,7 +11189,7 @@
         <v>307</v>
       </c>
       <c r="D21" s="9">
-        <v>1307</v>
+        <v>307</v>
       </c>
       <c r="E21" s="10">
         <v>163000</v>
@@ -11218,7 +11218,7 @@
         <v>308</v>
       </c>
       <c r="D22" s="9">
-        <v>1308</v>
+        <v>308</v>
       </c>
       <c r="E22" s="10">
         <v>163000</v>
@@ -11247,7 +11247,7 @@
         <v>401</v>
       </c>
       <c r="D23" s="9">
-        <v>1401</v>
+        <v>401</v>
       </c>
       <c r="E23" s="10">
         <v>163000</v>
@@ -11276,7 +11276,7 @@
         <v>402</v>
       </c>
       <c r="D24" s="9">
-        <v>1402</v>
+        <v>402</v>
       </c>
       <c r="E24" s="10">
         <v>163000</v>
@@ -11305,7 +11305,7 @@
         <v>403</v>
       </c>
       <c r="D25" s="9">
-        <v>1403</v>
+        <v>403</v>
       </c>
       <c r="E25" s="10">
         <v>163000</v>
@@ -11334,7 +11334,7 @@
         <v>404</v>
       </c>
       <c r="D26" s="9">
-        <v>1404</v>
+        <v>404</v>
       </c>
       <c r="E26" s="10">
         <v>163000</v>
@@ -11363,7 +11363,7 @@
         <v>405</v>
       </c>
       <c r="D27" s="9">
-        <v>1405</v>
+        <v>405</v>
       </c>
       <c r="E27" s="10">
         <v>163000</v>
@@ -11392,7 +11392,7 @@
         <v>406</v>
       </c>
       <c r="D28" s="9">
-        <v>1406</v>
+        <v>406</v>
       </c>
       <c r="E28" s="10">
         <v>163000</v>
@@ -11421,7 +11421,7 @@
         <v>407</v>
       </c>
       <c r="D29" s="9">
-        <v>1407</v>
+        <v>407</v>
       </c>
       <c r="E29" s="10">
         <v>163000</v>
@@ -11450,7 +11450,7 @@
         <v>408</v>
       </c>
       <c r="D30" s="9">
-        <v>1408</v>
+        <v>408</v>
       </c>
       <c r="E30" s="10">
         <v>163000</v>
@@ -11479,7 +11479,7 @@
         <v>501</v>
       </c>
       <c r="D31" s="9">
-        <v>1501</v>
+        <v>501</v>
       </c>
       <c r="E31" s="10">
         <v>163000</v>
@@ -11508,7 +11508,7 @@
         <v>502</v>
       </c>
       <c r="D32" s="9">
-        <v>1502</v>
+        <v>502</v>
       </c>
       <c r="E32" s="10">
         <v>163000</v>
@@ -11537,7 +11537,7 @@
         <v>503</v>
       </c>
       <c r="D33" s="9">
-        <v>1503</v>
+        <v>503</v>
       </c>
       <c r="E33" s="10">
         <v>163000</v>
@@ -11566,7 +11566,7 @@
         <v>504</v>
       </c>
       <c r="D34" s="9">
-        <v>1504</v>
+        <v>504</v>
       </c>
       <c r="E34" s="10">
         <v>163000</v>
@@ -11595,7 +11595,7 @@
         <v>505</v>
       </c>
       <c r="D35" s="9">
-        <v>1505</v>
+        <v>505</v>
       </c>
       <c r="E35" s="10">
         <v>163000</v>
@@ -11624,7 +11624,7 @@
         <v>506</v>
       </c>
       <c r="D36" s="9">
-        <v>1506</v>
+        <v>506</v>
       </c>
       <c r="E36" s="10">
         <v>163000</v>
@@ -11653,7 +11653,7 @@
         <v>507</v>
       </c>
       <c r="D37" s="9">
-        <v>1507</v>
+        <v>507</v>
       </c>
       <c r="E37" s="10">
         <v>163000</v>
@@ -11682,7 +11682,7 @@
         <v>508</v>
       </c>
       <c r="D38" s="9">
-        <v>1508</v>
+        <v>508</v>
       </c>
       <c r="E38" s="10">
         <v>163000</v>
@@ -11711,7 +11711,7 @@
         <v>601</v>
       </c>
       <c r="D39" s="9">
-        <v>1601</v>
+        <v>601</v>
       </c>
       <c r="E39" s="10">
         <v>163000</v>
@@ -11740,7 +11740,7 @@
         <v>502</v>
       </c>
       <c r="D40" s="9">
-        <v>1602</v>
+        <v>502</v>
       </c>
       <c r="E40" s="10">
         <v>163000</v>
@@ -11769,7 +11769,7 @@
         <v>603</v>
       </c>
       <c r="D41" s="9">
-        <v>1603</v>
+        <v>603</v>
       </c>
       <c r="E41" s="10">
         <v>163000</v>
@@ -11798,7 +11798,7 @@
         <v>604</v>
       </c>
       <c r="D42" s="9">
-        <v>1604</v>
+        <v>604</v>
       </c>
       <c r="E42" s="10">
         <v>163000</v>
@@ -11827,7 +11827,7 @@
         <v>605</v>
       </c>
       <c r="D43" s="9">
-        <v>1605</v>
+        <v>605</v>
       </c>
       <c r="E43" s="10">
         <v>163000</v>
@@ -11856,7 +11856,7 @@
         <v>606</v>
       </c>
       <c r="D44" s="9">
-        <v>1606</v>
+        <v>606</v>
       </c>
       <c r="E44" s="10">
         <v>163000</v>
@@ -11885,7 +11885,7 @@
         <v>607</v>
       </c>
       <c r="D45" s="9">
-        <v>1607</v>
+        <v>607</v>
       </c>
       <c r="E45" s="10">
         <v>163000</v>
@@ -11914,7 +11914,7 @@
         <v>608</v>
       </c>
       <c r="D46" s="9">
-        <v>1608</v>
+        <v>608</v>
       </c>
       <c r="E46" s="10">
         <v>163000</v>
@@ -11943,7 +11943,7 @@
         <v>701</v>
       </c>
       <c r="D47" s="9">
-        <v>1701</v>
+        <v>701</v>
       </c>
       <c r="E47" s="10">
         <v>163000</v>
@@ -11972,7 +11972,7 @@
         <v>702</v>
       </c>
       <c r="D48" s="9">
-        <v>1702</v>
+        <v>702</v>
       </c>
       <c r="E48" s="10">
         <v>163000</v>
@@ -12001,7 +12001,7 @@
         <v>703</v>
       </c>
       <c r="D49" s="9">
-        <v>1703</v>
+        <v>703</v>
       </c>
       <c r="E49" s="10">
         <v>163000</v>
@@ -12030,7 +12030,7 @@
         <v>704</v>
       </c>
       <c r="D50" s="9">
-        <v>1704</v>
+        <v>704</v>
       </c>
       <c r="E50" s="10">
         <v>163000</v>
@@ -12059,7 +12059,7 @@
         <v>705</v>
       </c>
       <c r="D51" s="9">
-        <v>1705</v>
+        <v>705</v>
       </c>
       <c r="E51" s="10">
         <v>163000</v>
@@ -12088,7 +12088,7 @@
         <v>706</v>
       </c>
       <c r="D52" s="9">
-        <v>1706</v>
+        <v>706</v>
       </c>
       <c r="E52" s="10">
         <v>163000</v>
@@ -12117,7 +12117,7 @@
         <v>707</v>
       </c>
       <c r="D53" s="9">
-        <v>1707</v>
+        <v>707</v>
       </c>
       <c r="E53" s="10">
         <v>163000</v>
@@ -12146,7 +12146,7 @@
         <v>708</v>
       </c>
       <c r="D54" s="9">
-        <v>1708</v>
+        <v>708</v>
       </c>
       <c r="E54" s="10">
         <v>163000</v>
@@ -12175,7 +12175,7 @@
         <v>801</v>
       </c>
       <c r="D55" s="9">
-        <v>1801</v>
+        <v>801</v>
       </c>
       <c r="E55" s="10">
         <v>163000</v>
@@ -12204,7 +12204,7 @@
         <v>802</v>
       </c>
       <c r="D56" s="9">
-        <v>1802</v>
+        <v>802</v>
       </c>
       <c r="E56" s="10">
         <v>163000</v>
@@ -12233,7 +12233,7 @@
         <v>803</v>
       </c>
       <c r="D57" s="9">
-        <v>1803</v>
+        <v>803</v>
       </c>
       <c r="E57" s="10">
         <v>163000</v>
@@ -12262,7 +12262,7 @@
         <v>804</v>
       </c>
       <c r="D58" s="9">
-        <v>1804</v>
+        <v>804</v>
       </c>
       <c r="E58" s="10">
         <v>163000</v>
@@ -12291,7 +12291,7 @@
         <v>805</v>
       </c>
       <c r="D59" s="9">
-        <v>1805</v>
+        <v>805</v>
       </c>
       <c r="E59" s="10">
         <v>163000</v>
@@ -12320,7 +12320,7 @@
         <v>806</v>
       </c>
       <c r="D60" s="9">
-        <v>1806</v>
+        <v>806</v>
       </c>
       <c r="E60" s="10">
         <v>163000</v>
@@ -12349,7 +12349,7 @@
         <v>807</v>
       </c>
       <c r="D61" s="9">
-        <v>1807</v>
+        <v>807</v>
       </c>
       <c r="E61" s="10">
         <v>163000</v>
@@ -12378,7 +12378,7 @@
         <v>808</v>
       </c>
       <c r="D62" s="9">
-        <v>1808</v>
+        <v>808</v>
       </c>
       <c r="E62" s="10">
         <v>163000</v>
@@ -12407,7 +12407,7 @@
         <v>901</v>
       </c>
       <c r="D63" s="9">
-        <v>1901</v>
+        <v>901</v>
       </c>
       <c r="E63" s="10">
         <v>163000</v>
@@ -12436,7 +12436,7 @@
         <v>902</v>
       </c>
       <c r="D64" s="9">
-        <v>1902</v>
+        <v>902</v>
       </c>
       <c r="E64" s="10">
         <v>163000</v>
@@ -12465,7 +12465,7 @@
         <v>903</v>
       </c>
       <c r="D65" s="9">
-        <v>1903</v>
+        <v>903</v>
       </c>
       <c r="E65" s="10">
         <v>163000</v>
@@ -12494,7 +12494,7 @@
         <v>904</v>
       </c>
       <c r="D66" s="9">
-        <v>1904</v>
+        <v>904</v>
       </c>
       <c r="E66" s="10">
         <v>163000</v>
@@ -12523,7 +12523,7 @@
         <v>905</v>
       </c>
       <c r="D67" s="9">
-        <v>1905</v>
+        <v>905</v>
       </c>
       <c r="E67" s="10">
         <v>163000</v>
@@ -12552,7 +12552,7 @@
         <v>906</v>
       </c>
       <c r="D68" s="9">
-        <v>1906</v>
+        <v>906</v>
       </c>
       <c r="E68" s="10">
         <v>163000</v>
@@ -12581,7 +12581,7 @@
         <v>907</v>
       </c>
       <c r="D69" s="9">
-        <v>1907</v>
+        <v>907</v>
       </c>
       <c r="E69" s="10">
         <v>163000</v>
@@ -12610,7 +12610,7 @@
         <v>908</v>
       </c>
       <c r="D70" s="9">
-        <v>1908</v>
+        <v>908</v>
       </c>
       <c r="E70" s="10">
         <v>163000</v>
@@ -12639,7 +12639,7 @@
         <v>1001</v>
       </c>
       <c r="D71" s="9">
-        <v>11001</v>
+        <v>1001</v>
       </c>
       <c r="E71" s="10">
         <v>163000</v>
@@ -12668,7 +12668,7 @@
         <v>1002</v>
       </c>
       <c r="D72" s="9">
-        <v>11002</v>
+        <v>1002</v>
       </c>
       <c r="E72" s="10">
         <v>163000</v>
@@ -12697,7 +12697,7 @@
         <v>1003</v>
       </c>
       <c r="D73" s="9">
-        <v>11003</v>
+        <v>1003</v>
       </c>
       <c r="E73" s="10">
         <v>163000</v>
@@ -12726,7 +12726,7 @@
         <v>1004</v>
       </c>
       <c r="D74" s="9">
-        <v>11004</v>
+        <v>1004</v>
       </c>
       <c r="E74" s="10">
         <v>163000</v>
@@ -12755,7 +12755,7 @@
         <v>1005</v>
       </c>
       <c r="D75" s="9">
-        <v>11005</v>
+        <v>1005</v>
       </c>
       <c r="E75" s="10">
         <v>163000</v>
@@ -12784,7 +12784,7 @@
         <v>1006</v>
       </c>
       <c r="D76" s="9">
-        <v>11006</v>
+        <v>1006</v>
       </c>
       <c r="E76" s="10">
         <v>163000</v>
@@ -12813,7 +12813,7 @@
         <v>1007</v>
       </c>
       <c r="D77" s="9">
-        <v>11007</v>
+        <v>1007</v>
       </c>
       <c r="E77" s="10">
         <v>163000</v>
@@ -12842,7 +12842,7 @@
         <v>1008</v>
       </c>
       <c r="D78" s="9">
-        <v>11008</v>
+        <v>1008</v>
       </c>
       <c r="E78" s="10">
         <v>163000</v>
@@ -12871,7 +12871,7 @@
         <v>1101</v>
       </c>
       <c r="D79" s="9">
-        <v>11101</v>
+        <v>1101</v>
       </c>
       <c r="E79" s="10">
         <v>163000</v>
@@ -12900,7 +12900,7 @@
         <v>1102</v>
       </c>
       <c r="D80" s="9">
-        <v>11102</v>
+        <v>1102</v>
       </c>
       <c r="E80" s="10">
         <v>163000</v>
@@ -12929,7 +12929,7 @@
         <v>1103</v>
       </c>
       <c r="D81" s="9">
-        <v>11103</v>
+        <v>1103</v>
       </c>
       <c r="E81" s="10">
         <v>163000</v>
@@ -12958,7 +12958,7 @@
         <v>1104</v>
       </c>
       <c r="D82" s="9">
-        <v>11104</v>
+        <v>1104</v>
       </c>
       <c r="E82" s="10">
         <v>163000</v>
@@ -12987,7 +12987,7 @@
         <v>1105</v>
       </c>
       <c r="D83" s="9">
-        <v>11105</v>
+        <v>1105</v>
       </c>
       <c r="E83" s="10">
         <v>163000</v>
@@ -13016,7 +13016,7 @@
         <v>1106</v>
       </c>
       <c r="D84" s="9">
-        <v>11106</v>
+        <v>1106</v>
       </c>
       <c r="E84" s="10">
         <v>163000</v>
@@ -13045,7 +13045,7 @@
         <v>1107</v>
       </c>
       <c r="D85" s="9">
-        <v>11107</v>
+        <v>1107</v>
       </c>
       <c r="E85" s="10">
         <v>163000</v>
@@ -13074,7 +13074,7 @@
         <v>1108</v>
       </c>
       <c r="D86" s="9">
-        <v>11108</v>
+        <v>1108</v>
       </c>
       <c r="E86" s="10">
         <v>163000</v>
@@ -13103,7 +13103,7 @@
         <v>1201</v>
       </c>
       <c r="D87" s="9">
-        <v>11201</v>
+        <v>1201</v>
       </c>
       <c r="E87" s="10">
         <v>163000</v>
@@ -13132,7 +13132,7 @@
         <v>1202</v>
       </c>
       <c r="D88" s="9">
-        <v>11202</v>
+        <v>1202</v>
       </c>
       <c r="E88" s="10">
         <v>163000</v>
@@ -13161,7 +13161,7 @@
         <v>1203</v>
       </c>
       <c r="D89" s="9">
-        <v>11203</v>
+        <v>1203</v>
       </c>
       <c r="E89" s="10">
         <v>163000</v>
@@ -13190,7 +13190,7 @@
         <v>1204</v>
       </c>
       <c r="D90" s="9">
-        <v>11204</v>
+        <v>1204</v>
       </c>
       <c r="E90" s="10">
         <v>163000</v>
@@ -13219,7 +13219,7 @@
         <v>1205</v>
       </c>
       <c r="D91" s="9">
-        <v>11205</v>
+        <v>1205</v>
       </c>
       <c r="E91" s="10">
         <v>163000</v>
@@ -13248,7 +13248,7 @@
         <v>1206</v>
       </c>
       <c r="D92" s="9">
-        <v>11206</v>
+        <v>1206</v>
       </c>
       <c r="E92" s="10">
         <v>163000</v>
@@ -13277,7 +13277,7 @@
         <v>1207</v>
       </c>
       <c r="D93" s="9">
-        <v>11207</v>
+        <v>1207</v>
       </c>
       <c r="E93" s="10">
         <v>163000</v>
@@ -13306,7 +13306,7 @@
         <v>1208</v>
       </c>
       <c r="D94" s="9">
-        <v>11208</v>
+        <v>1208</v>
       </c>
       <c r="E94" s="10">
         <v>163000</v>
@@ -13335,7 +13335,7 @@
         <v>1301</v>
       </c>
       <c r="D95" s="9">
-        <v>11301</v>
+        <v>1301</v>
       </c>
       <c r="E95" s="10">
         <v>163000</v>
@@ -13364,7 +13364,7 @@
         <v>1302</v>
       </c>
       <c r="D96" s="9">
-        <v>11302</v>
+        <v>1302</v>
       </c>
       <c r="E96" s="10">
         <v>163000</v>
@@ -13393,7 +13393,7 @@
         <v>1303</v>
       </c>
       <c r="D97" s="9">
-        <v>11303</v>
+        <v>1303</v>
       </c>
       <c r="E97" s="10">
         <v>163000</v>
@@ -13422,7 +13422,7 @@
         <v>1304</v>
       </c>
       <c r="D98" s="9">
-        <v>11304</v>
+        <v>1304</v>
       </c>
       <c r="E98" s="10">
         <v>163000</v>
@@ -13451,7 +13451,7 @@
         <v>1305</v>
       </c>
       <c r="D99" s="9">
-        <v>11305</v>
+        <v>1305</v>
       </c>
       <c r="E99" s="10">
         <v>163000</v>
@@ -13480,7 +13480,7 @@
         <v>1306</v>
       </c>
       <c r="D100" s="9">
-        <v>11306</v>
+        <v>1306</v>
       </c>
       <c r="E100" s="10">
         <v>163000</v>
@@ -13509,7 +13509,7 @@
         <v>1307</v>
       </c>
       <c r="D101" s="9">
-        <v>11307</v>
+        <v>1307</v>
       </c>
       <c r="E101" s="10">
         <v>163000</v>
@@ -13538,7 +13538,7 @@
         <v>1308</v>
       </c>
       <c r="D102" s="9">
-        <v>11308</v>
+        <v>1308</v>
       </c>
       <c r="E102" s="10">
         <v>163000</v>
@@ -13567,7 +13567,7 @@
         <v>1401</v>
       </c>
       <c r="D103" s="9">
-        <v>11401</v>
+        <v>1401</v>
       </c>
       <c r="E103" s="10">
         <v>163000</v>
@@ -13596,7 +13596,7 @@
         <v>1402</v>
       </c>
       <c r="D104" s="9">
-        <v>11402</v>
+        <v>1402</v>
       </c>
       <c r="E104" s="10">
         <v>163000</v>
@@ -13625,7 +13625,7 @@
         <v>1403</v>
       </c>
       <c r="D105" s="9">
-        <v>11403</v>
+        <v>1403</v>
       </c>
       <c r="E105" s="10">
         <v>163000</v>
@@ -13654,7 +13654,7 @@
         <v>1404</v>
       </c>
       <c r="D106" s="9">
-        <v>11404</v>
+        <v>1404</v>
       </c>
       <c r="E106" s="10">
         <v>163000</v>
@@ -13683,7 +13683,7 @@
         <v>1405</v>
       </c>
       <c r="D107" s="9">
-        <v>11405</v>
+        <v>1405</v>
       </c>
       <c r="E107" s="10">
         <v>163000</v>
@@ -13712,7 +13712,7 @@
         <v>1406</v>
       </c>
       <c r="D108" s="9">
-        <v>11406</v>
+        <v>1406</v>
       </c>
       <c r="E108" s="10">
         <v>163000</v>
@@ -13741,7 +13741,7 @@
         <v>1406</v>
       </c>
       <c r="D109" s="9">
-        <v>11407</v>
+        <v>1406</v>
       </c>
       <c r="E109" s="10">
         <v>163000</v>
@@ -13770,7 +13770,7 @@
         <v>1408</v>
       </c>
       <c r="D110" s="9">
-        <v>11408</v>
+        <v>1408</v>
       </c>
       <c r="E110" s="10">
         <v>163000</v>
@@ -13799,7 +13799,7 @@
         <v>1501</v>
       </c>
       <c r="D111" s="9">
-        <v>11501</v>
+        <v>1501</v>
       </c>
       <c r="E111" s="10">
         <v>163000</v>
@@ -13828,7 +13828,7 @@
         <v>1502</v>
       </c>
       <c r="D112" s="9">
-        <v>11502</v>
+        <v>1502</v>
       </c>
       <c r="E112" s="10">
         <v>163000</v>
@@ -13857,7 +13857,7 @@
         <v>1503</v>
       </c>
       <c r="D113" s="9">
-        <v>11503</v>
+        <v>1503</v>
       </c>
       <c r="E113" s="10">
         <v>163000</v>
@@ -13886,7 +13886,7 @@
         <v>1504</v>
       </c>
       <c r="D114" s="9">
-        <v>11504</v>
+        <v>1504</v>
       </c>
       <c r="E114" s="10">
         <v>163000</v>
@@ -13915,7 +13915,7 @@
         <v>1505</v>
       </c>
       <c r="D115" s="9">
-        <v>11505</v>
+        <v>1505</v>
       </c>
       <c r="E115" s="10">
         <v>163000</v>
@@ -13944,7 +13944,7 @@
         <v>1506</v>
       </c>
       <c r="D116" s="9">
-        <v>11506</v>
+        <v>1506</v>
       </c>
       <c r="E116" s="10">
         <v>163000</v>
@@ -13973,7 +13973,7 @@
         <v>1507</v>
       </c>
       <c r="D117" s="9">
-        <v>11507</v>
+        <v>1507</v>
       </c>
       <c r="E117" s="10">
         <v>163000</v>
@@ -14002,7 +14002,7 @@
         <v>1508</v>
       </c>
       <c r="D118" s="9">
-        <v>11508</v>
+        <v>1508</v>
       </c>
       <c r="E118" s="10">
         <v>163000</v>
@@ -14031,7 +14031,7 @@
         <v>1</v>
       </c>
       <c r="D119" s="9">
-        <v>2001</v>
+        <v>1</v>
       </c>
       <c r="E119" s="10">
         <v>163000</v>
@@ -14060,7 +14060,7 @@
         <v>8</v>
       </c>
       <c r="D120" s="9">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="E120" s="10">
         <v>163000</v>
@@ -14089,7 +14089,7 @@
         <v>101</v>
       </c>
       <c r="D121" s="9">
-        <v>2101</v>
+        <v>101</v>
       </c>
       <c r="E121" s="10">
         <v>163000</v>
@@ -14118,7 +14118,7 @@
         <v>102</v>
       </c>
       <c r="D122" s="9">
-        <v>2102</v>
+        <v>102</v>
       </c>
       <c r="E122" s="10">
         <v>163000</v>
@@ -14147,7 +14147,7 @@
         <v>103</v>
       </c>
       <c r="D123" s="9">
-        <v>2103</v>
+        <v>103</v>
       </c>
       <c r="E123" s="10">
         <v>163000</v>
@@ -14176,7 +14176,7 @@
         <v>106</v>
       </c>
       <c r="D124" s="9">
-        <v>2106</v>
+        <v>106</v>
       </c>
       <c r="E124" s="10">
         <v>163000</v>
@@ -14205,7 +14205,7 @@
         <v>107</v>
       </c>
       <c r="D125" s="9">
-        <v>2107</v>
+        <v>107</v>
       </c>
       <c r="E125" s="10">
         <v>163000</v>
@@ -14234,7 +14234,7 @@
         <v>108</v>
       </c>
       <c r="D126" s="9">
-        <v>2108</v>
+        <v>108</v>
       </c>
       <c r="E126" s="10">
         <v>163000</v>
@@ -14263,7 +14263,7 @@
         <v>201</v>
       </c>
       <c r="D127" s="9">
-        <v>2201</v>
+        <v>201</v>
       </c>
       <c r="E127" s="10">
         <v>163000</v>
@@ -14292,7 +14292,7 @@
         <v>202</v>
       </c>
       <c r="D128" s="9">
-        <v>2202</v>
+        <v>202</v>
       </c>
       <c r="E128" s="10">
         <v>163000</v>
@@ -14321,7 +14321,7 @@
         <v>203</v>
       </c>
       <c r="D129" s="9">
-        <v>2203</v>
+        <v>203</v>
       </c>
       <c r="E129" s="10">
         <v>163000</v>
@@ -14350,7 +14350,7 @@
         <v>204</v>
       </c>
       <c r="D130" s="9">
-        <v>2204</v>
+        <v>204</v>
       </c>
       <c r="E130" s="10">
         <v>163000</v>
@@ -14379,7 +14379,7 @@
         <v>205</v>
       </c>
       <c r="D131" s="9">
-        <v>2205</v>
+        <v>205</v>
       </c>
       <c r="E131" s="10">
         <v>163000</v>
@@ -14408,7 +14408,7 @@
         <v>206</v>
       </c>
       <c r="D132" s="9">
-        <v>2206</v>
+        <v>206</v>
       </c>
       <c r="E132" s="10">
         <v>163000</v>
@@ -14437,7 +14437,7 @@
         <v>207</v>
       </c>
       <c r="D133" s="9">
-        <v>2207</v>
+        <v>207</v>
       </c>
       <c r="E133" s="10">
         <v>163000</v>
@@ -14466,7 +14466,7 @@
         <v>208</v>
       </c>
       <c r="D134" s="9">
-        <v>2208</v>
+        <v>208</v>
       </c>
       <c r="E134" s="10">
         <v>163000</v>
@@ -14495,7 +14495,7 @@
         <v>301</v>
       </c>
       <c r="D135" s="9">
-        <v>2301</v>
+        <v>301</v>
       </c>
       <c r="E135" s="10">
         <v>163000</v>
@@ -14524,7 +14524,7 @@
         <v>302</v>
       </c>
       <c r="D136" s="9">
-        <v>2302</v>
+        <v>302</v>
       </c>
       <c r="E136" s="10">
         <v>163000</v>
@@ -14553,7 +14553,7 @@
         <v>303</v>
       </c>
       <c r="D137" s="9">
-        <v>2303</v>
+        <v>303</v>
       </c>
       <c r="E137" s="10">
         <v>163000</v>
@@ -14582,7 +14582,7 @@
         <v>304</v>
       </c>
       <c r="D138" s="9">
-        <v>2304</v>
+        <v>304</v>
       </c>
       <c r="E138" s="10">
         <v>163000</v>
@@ -14611,7 +14611,7 @@
         <v>305</v>
       </c>
       <c r="D139" s="9">
-        <v>2305</v>
+        <v>305</v>
       </c>
       <c r="E139" s="10">
         <v>163000</v>
@@ -14640,7 +14640,7 @@
         <v>306</v>
       </c>
       <c r="D140" s="9">
-        <v>2306</v>
+        <v>306</v>
       </c>
       <c r="E140" s="10">
         <v>163000</v>
@@ -14669,7 +14669,7 @@
         <v>307</v>
       </c>
       <c r="D141" s="9">
-        <v>2307</v>
+        <v>307</v>
       </c>
       <c r="E141" s="10">
         <v>163000</v>
@@ -14698,7 +14698,7 @@
         <v>308</v>
       </c>
       <c r="D142" s="9">
-        <v>2308</v>
+        <v>308</v>
       </c>
       <c r="E142" s="10">
         <v>163000</v>
@@ -14727,7 +14727,7 @@
         <v>401</v>
       </c>
       <c r="D143" s="9">
-        <v>2401</v>
+        <v>401</v>
       </c>
       <c r="E143" s="10">
         <v>163000</v>
@@ -14756,7 +14756,7 @@
         <v>402</v>
       </c>
       <c r="D144" s="9">
-        <v>2402</v>
+        <v>402</v>
       </c>
       <c r="E144" s="10">
         <v>163000</v>
@@ -14785,7 +14785,7 @@
         <v>403</v>
       </c>
       <c r="D145" s="9">
-        <v>2403</v>
+        <v>403</v>
       </c>
       <c r="E145" s="10">
         <v>163000</v>
@@ -14814,7 +14814,7 @@
         <v>404</v>
       </c>
       <c r="D146" s="9">
-        <v>2404</v>
+        <v>404</v>
       </c>
       <c r="E146" s="10">
         <v>163000</v>
@@ -14843,7 +14843,7 @@
         <v>405</v>
       </c>
       <c r="D147" s="9">
-        <v>2405</v>
+        <v>405</v>
       </c>
       <c r="E147" s="10">
         <v>163000</v>
@@ -14872,7 +14872,7 @@
         <v>406</v>
       </c>
       <c r="D148" s="9">
-        <v>2406</v>
+        <v>406</v>
       </c>
       <c r="E148" s="10">
         <v>163000</v>
@@ -14901,7 +14901,7 @@
         <v>407</v>
       </c>
       <c r="D149" s="9">
-        <v>2407</v>
+        <v>407</v>
       </c>
       <c r="E149" s="10">
         <v>163000</v>
@@ -14930,7 +14930,7 @@
         <v>408</v>
       </c>
       <c r="D150" s="9">
-        <v>2408</v>
+        <v>408</v>
       </c>
       <c r="E150" s="10">
         <v>163000</v>
@@ -14959,7 +14959,7 @@
         <v>501</v>
       </c>
       <c r="D151" s="9">
-        <v>2501</v>
+        <v>501</v>
       </c>
       <c r="E151" s="10">
         <v>163000</v>
@@ -14988,7 +14988,7 @@
         <v>502</v>
       </c>
       <c r="D152" s="9">
-        <v>2502</v>
+        <v>502</v>
       </c>
       <c r="E152" s="10">
         <v>163000</v>
@@ -15017,7 +15017,7 @@
         <v>503</v>
       </c>
       <c r="D153" s="9">
-        <v>2503</v>
+        <v>503</v>
       </c>
       <c r="E153" s="10">
         <v>163000</v>
@@ -15046,7 +15046,7 @@
         <v>504</v>
       </c>
       <c r="D154" s="9">
-        <v>2504</v>
+        <v>504</v>
       </c>
       <c r="E154" s="10">
         <v>163000</v>
@@ -15075,7 +15075,7 @@
         <v>505</v>
       </c>
       <c r="D155" s="9">
-        <v>2505</v>
+        <v>505</v>
       </c>
       <c r="E155" s="10">
         <v>163000</v>
@@ -15104,7 +15104,7 @@
         <v>506</v>
       </c>
       <c r="D156" s="9">
-        <v>2506</v>
+        <v>506</v>
       </c>
       <c r="E156" s="10">
         <v>163000</v>
@@ -15133,7 +15133,7 @@
         <v>507</v>
       </c>
       <c r="D157" s="9">
-        <v>2507</v>
+        <v>507</v>
       </c>
       <c r="E157" s="10">
         <v>163000</v>
@@ -15162,7 +15162,7 @@
         <v>508</v>
       </c>
       <c r="D158" s="9">
-        <v>2508</v>
+        <v>508</v>
       </c>
       <c r="E158" s="10">
         <v>163000</v>
@@ -15191,7 +15191,7 @@
         <v>601</v>
       </c>
       <c r="D159" s="9">
-        <v>2601</v>
+        <v>601</v>
       </c>
       <c r="E159" s="10">
         <v>163000</v>
@@ -15220,7 +15220,7 @@
         <v>502</v>
       </c>
       <c r="D160" s="9">
-        <v>2602</v>
+        <v>502</v>
       </c>
       <c r="E160" s="10">
         <v>163000</v>
@@ -15249,7 +15249,7 @@
         <v>603</v>
       </c>
       <c r="D161" s="9">
-        <v>2603</v>
+        <v>603</v>
       </c>
       <c r="E161" s="10">
         <v>163000</v>
@@ -15278,7 +15278,7 @@
         <v>604</v>
       </c>
       <c r="D162" s="9">
-        <v>2604</v>
+        <v>604</v>
       </c>
       <c r="E162" s="10">
         <v>163000</v>
@@ -15307,7 +15307,7 @@
         <v>605</v>
       </c>
       <c r="D163" s="9">
-        <v>2605</v>
+        <v>605</v>
       </c>
       <c r="E163" s="10">
         <v>163000</v>
@@ -15336,7 +15336,7 @@
         <v>606</v>
       </c>
       <c r="D164" s="9">
-        <v>2606</v>
+        <v>606</v>
       </c>
       <c r="E164" s="10">
         <v>163000</v>
@@ -15365,7 +15365,7 @@
         <v>607</v>
       </c>
       <c r="D165" s="9">
-        <v>2607</v>
+        <v>607</v>
       </c>
       <c r="E165" s="10">
         <v>163000</v>
@@ -15394,7 +15394,7 @@
         <v>608</v>
       </c>
       <c r="D166" s="9">
-        <v>2608</v>
+        <v>608</v>
       </c>
       <c r="E166" s="10">
         <v>163000</v>
@@ -15423,7 +15423,7 @@
         <v>701</v>
       </c>
       <c r="D167" s="9">
-        <v>2701</v>
+        <v>701</v>
       </c>
       <c r="E167" s="10">
         <v>163000</v>
@@ -15452,7 +15452,7 @@
         <v>702</v>
       </c>
       <c r="D168" s="9">
-        <v>2702</v>
+        <v>702</v>
       </c>
       <c r="E168" s="10">
         <v>163000</v>
@@ -15481,7 +15481,7 @@
         <v>703</v>
       </c>
       <c r="D169" s="9">
-        <v>2703</v>
+        <v>703</v>
       </c>
       <c r="E169" s="10">
         <v>163000</v>
@@ -15510,7 +15510,7 @@
         <v>704</v>
       </c>
       <c r="D170" s="9">
-        <v>2704</v>
+        <v>704</v>
       </c>
       <c r="E170" s="10">
         <v>163000</v>
@@ -15539,7 +15539,7 @@
         <v>705</v>
       </c>
       <c r="D171" s="9">
-        <v>2705</v>
+        <v>705</v>
       </c>
       <c r="E171" s="10">
         <v>163000</v>
@@ -15568,7 +15568,7 @@
         <v>706</v>
       </c>
       <c r="D172" s="9">
-        <v>2706</v>
+        <v>706</v>
       </c>
       <c r="E172" s="10">
         <v>163000</v>
@@ -15597,7 +15597,7 @@
         <v>707</v>
       </c>
       <c r="D173" s="9">
-        <v>2707</v>
+        <v>707</v>
       </c>
       <c r="E173" s="10">
         <v>163000</v>
@@ -15626,7 +15626,7 @@
         <v>708</v>
       </c>
       <c r="D174" s="9">
-        <v>2708</v>
+        <v>708</v>
       </c>
       <c r="E174" s="10">
         <v>163000</v>
@@ -15655,7 +15655,7 @@
         <v>801</v>
       </c>
       <c r="D175" s="9">
-        <v>2801</v>
+        <v>801</v>
       </c>
       <c r="E175" s="10">
         <v>163000</v>
@@ -15684,7 +15684,7 @@
         <v>802</v>
       </c>
       <c r="D176" s="9">
-        <v>2802</v>
+        <v>802</v>
       </c>
       <c r="E176" s="10">
         <v>163000</v>
@@ -15713,7 +15713,7 @@
         <v>803</v>
       </c>
       <c r="D177" s="9">
-        <v>2803</v>
+        <v>803</v>
       </c>
       <c r="E177" s="10">
         <v>163000</v>
@@ -15742,7 +15742,7 @@
         <v>804</v>
       </c>
       <c r="D178" s="9">
-        <v>2804</v>
+        <v>804</v>
       </c>
       <c r="E178" s="10">
         <v>163000</v>
@@ -15771,7 +15771,7 @@
         <v>805</v>
       </c>
       <c r="D179" s="9">
-        <v>2805</v>
+        <v>805</v>
       </c>
       <c r="E179" s="10">
         <v>163000</v>
@@ -15800,7 +15800,7 @@
         <v>806</v>
       </c>
       <c r="D180" s="9">
-        <v>2806</v>
+        <v>806</v>
       </c>
       <c r="E180" s="10">
         <v>163000</v>
@@ -15829,7 +15829,7 @@
         <v>807</v>
       </c>
       <c r="D181" s="9">
-        <v>2807</v>
+        <v>807</v>
       </c>
       <c r="E181" s="10">
         <v>163000</v>
@@ -15858,7 +15858,7 @@
         <v>808</v>
       </c>
       <c r="D182" s="9">
-        <v>2808</v>
+        <v>808</v>
       </c>
       <c r="E182" s="10">
         <v>163000</v>
@@ -15887,7 +15887,7 @@
         <v>901</v>
       </c>
       <c r="D183" s="9">
-        <v>2901</v>
+        <v>901</v>
       </c>
       <c r="E183" s="10">
         <v>163000</v>
@@ -15916,7 +15916,7 @@
         <v>902</v>
       </c>
       <c r="D184" s="9">
-        <v>2902</v>
+        <v>902</v>
       </c>
       <c r="E184" s="10">
         <v>163000</v>
@@ -15945,7 +15945,7 @@
         <v>903</v>
       </c>
       <c r="D185" s="9">
-        <v>2903</v>
+        <v>903</v>
       </c>
       <c r="E185" s="10">
         <v>163000</v>
@@ -15974,7 +15974,7 @@
         <v>904</v>
       </c>
       <c r="D186" s="9">
-        <v>2904</v>
+        <v>904</v>
       </c>
       <c r="E186" s="10">
         <v>163000</v>
@@ -16003,7 +16003,7 @@
         <v>905</v>
       </c>
       <c r="D187" s="9">
-        <v>2905</v>
+        <v>905</v>
       </c>
       <c r="E187" s="10">
         <v>163000</v>
@@ -16032,7 +16032,7 @@
         <v>906</v>
       </c>
       <c r="D188" s="9">
-        <v>2906</v>
+        <v>906</v>
       </c>
       <c r="E188" s="10">
         <v>163000</v>
@@ -16061,7 +16061,7 @@
         <v>907</v>
       </c>
       <c r="D189" s="9">
-        <v>2907</v>
+        <v>907</v>
       </c>
       <c r="E189" s="10">
         <v>163000</v>
@@ -16090,7 +16090,7 @@
         <v>908</v>
       </c>
       <c r="D190" s="9">
-        <v>2908</v>
+        <v>908</v>
       </c>
       <c r="E190" s="10">
         <v>163000</v>
@@ -16119,7 +16119,7 @@
         <v>1001</v>
       </c>
       <c r="D191" s="9">
-        <v>21001</v>
+        <v>1001</v>
       </c>
       <c r="E191" s="10">
         <v>163000</v>
@@ -16148,7 +16148,7 @@
         <v>1002</v>
       </c>
       <c r="D192" s="9">
-        <v>21002</v>
+        <v>1002</v>
       </c>
       <c r="E192" s="10">
         <v>163000</v>
@@ -16177,7 +16177,7 @@
         <v>1003</v>
       </c>
       <c r="D193" s="9">
-        <v>21003</v>
+        <v>1003</v>
       </c>
       <c r="E193" s="10">
         <v>163000</v>
@@ -16206,7 +16206,7 @@
         <v>1004</v>
       </c>
       <c r="D194" s="9">
-        <v>21004</v>
+        <v>1004</v>
       </c>
       <c r="E194" s="10">
         <v>163000</v>
@@ -16235,7 +16235,7 @@
         <v>1005</v>
       </c>
       <c r="D195" s="9">
-        <v>21005</v>
+        <v>1005</v>
       </c>
       <c r="E195" s="10">
         <v>163000</v>
@@ -16264,7 +16264,7 @@
         <v>1006</v>
       </c>
       <c r="D196" s="9">
-        <v>21006</v>
+        <v>1006</v>
       </c>
       <c r="E196" s="10">
         <v>163000</v>
@@ -16293,7 +16293,7 @@
         <v>1007</v>
       </c>
       <c r="D197" s="9">
-        <v>21007</v>
+        <v>1007</v>
       </c>
       <c r="E197" s="10">
         <v>163000</v>
@@ -16322,7 +16322,7 @@
         <v>1008</v>
       </c>
       <c r="D198" s="9">
-        <v>21008</v>
+        <v>1008</v>
       </c>
       <c r="E198" s="10">
         <v>163000</v>
@@ -16351,7 +16351,7 @@
         <v>1101</v>
       </c>
       <c r="D199" s="9">
-        <v>21101</v>
+        <v>1101</v>
       </c>
       <c r="E199" s="10">
         <v>163000</v>
@@ -16380,7 +16380,7 @@
         <v>1102</v>
       </c>
       <c r="D200" s="9">
-        <v>21102</v>
+        <v>1102</v>
       </c>
       <c r="E200" s="10">
         <v>163000</v>
@@ -16409,7 +16409,7 @@
         <v>1103</v>
       </c>
       <c r="D201" s="9">
-        <v>21103</v>
+        <v>1103</v>
       </c>
       <c r="E201" s="10">
         <v>163000</v>
@@ -16438,7 +16438,7 @@
         <v>1104</v>
       </c>
       <c r="D202" s="9">
-        <v>21104</v>
+        <v>1104</v>
       </c>
       <c r="E202" s="10">
         <v>163000</v>
@@ -16467,7 +16467,7 @@
         <v>1105</v>
       </c>
       <c r="D203" s="9">
-        <v>21105</v>
+        <v>1105</v>
       </c>
       <c r="E203" s="10">
         <v>163000</v>
@@ -16496,7 +16496,7 @@
         <v>1106</v>
       </c>
       <c r="D204" s="9">
-        <v>21106</v>
+        <v>1106</v>
       </c>
       <c r="E204" s="10">
         <v>163000</v>
@@ -16525,7 +16525,7 @@
         <v>1107</v>
       </c>
       <c r="D205" s="9">
-        <v>21107</v>
+        <v>1107</v>
       </c>
       <c r="E205" s="10">
         <v>163000</v>
@@ -16554,7 +16554,7 @@
         <v>1108</v>
       </c>
       <c r="D206" s="9">
-        <v>21108</v>
+        <v>1108</v>
       </c>
       <c r="E206" s="10">
         <v>163000</v>
@@ -16583,7 +16583,7 @@
         <v>1201</v>
       </c>
       <c r="D207" s="9">
-        <v>21201</v>
+        <v>1201</v>
       </c>
       <c r="E207" s="10">
         <v>163000</v>
@@ -16612,7 +16612,7 @@
         <v>1202</v>
       </c>
       <c r="D208" s="9">
-        <v>21202</v>
+        <v>1202</v>
       </c>
       <c r="E208" s="10">
         <v>163000</v>
@@ -16641,7 +16641,7 @@
         <v>1203</v>
       </c>
       <c r="D209" s="9">
-        <v>21203</v>
+        <v>1203</v>
       </c>
       <c r="E209" s="10">
         <v>163000</v>
@@ -16670,7 +16670,7 @@
         <v>1204</v>
       </c>
       <c r="D210" s="9">
-        <v>21204</v>
+        <v>1204</v>
       </c>
       <c r="E210" s="10">
         <v>163000</v>
@@ -16699,7 +16699,7 @@
         <v>1205</v>
       </c>
       <c r="D211" s="9">
-        <v>21205</v>
+        <v>1205</v>
       </c>
       <c r="E211" s="10">
         <v>163000</v>
@@ -16728,7 +16728,7 @@
         <v>1206</v>
       </c>
       <c r="D212" s="9">
-        <v>21206</v>
+        <v>1206</v>
       </c>
       <c r="E212" s="10">
         <v>163000</v>
@@ -16757,7 +16757,7 @@
         <v>1207</v>
       </c>
       <c r="D213" s="9">
-        <v>21207</v>
+        <v>1207</v>
       </c>
       <c r="E213" s="10">
         <v>163000</v>
@@ -16786,7 +16786,7 @@
         <v>1208</v>
       </c>
       <c r="D214" s="9">
-        <v>21208</v>
+        <v>1208</v>
       </c>
       <c r="E214" s="10">
         <v>163000</v>
@@ -16815,7 +16815,7 @@
         <v>1301</v>
       </c>
       <c r="D215" s="9">
-        <v>21301</v>
+        <v>1301</v>
       </c>
       <c r="E215" s="10">
         <v>163000</v>
@@ -16844,7 +16844,7 @@
         <v>1302</v>
       </c>
       <c r="D216" s="9">
-        <v>21302</v>
+        <v>1302</v>
       </c>
       <c r="E216" s="10">
         <v>163000</v>
@@ -16873,7 +16873,7 @@
         <v>1303</v>
       </c>
       <c r="D217" s="9">
-        <v>21303</v>
+        <v>1303</v>
       </c>
       <c r="E217" s="10">
         <v>163000</v>
@@ -16902,7 +16902,7 @@
         <v>1304</v>
       </c>
       <c r="D218" s="9">
-        <v>21304</v>
+        <v>1304</v>
       </c>
       <c r="E218" s="10">
         <v>163000</v>
@@ -16931,7 +16931,7 @@
         <v>1305</v>
       </c>
       <c r="D219" s="9">
-        <v>21305</v>
+        <v>1305</v>
       </c>
       <c r="E219" s="10">
         <v>163000</v>
@@ -16960,7 +16960,7 @@
         <v>1306</v>
       </c>
       <c r="D220" s="9">
-        <v>21306</v>
+        <v>1306</v>
       </c>
       <c r="E220" s="10">
         <v>163000</v>
@@ -16989,7 +16989,7 @@
         <v>1307</v>
       </c>
       <c r="D221" s="9">
-        <v>21307</v>
+        <v>1307</v>
       </c>
       <c r="E221" s="10">
         <v>163000</v>
@@ -17018,7 +17018,7 @@
         <v>1308</v>
       </c>
       <c r="D222" s="9">
-        <v>21308</v>
+        <v>1308</v>
       </c>
       <c r="E222" s="10">
         <v>163000</v>
@@ -17047,7 +17047,7 @@
         <v>1401</v>
       </c>
       <c r="D223" s="9">
-        <v>21401</v>
+        <v>1401</v>
       </c>
       <c r="E223" s="10">
         <v>163000</v>
@@ -17076,7 +17076,7 @@
         <v>1402</v>
       </c>
       <c r="D224" s="9">
-        <v>21402</v>
+        <v>1402</v>
       </c>
       <c r="E224" s="10">
         <v>163000</v>
@@ -17105,7 +17105,7 @@
         <v>1403</v>
       </c>
       <c r="D225" s="9">
-        <v>21403</v>
+        <v>1403</v>
       </c>
       <c r="E225" s="10">
         <v>163000</v>
@@ -17134,7 +17134,7 @@
         <v>1404</v>
       </c>
       <c r="D226" s="9">
-        <v>21404</v>
+        <v>1404</v>
       </c>
       <c r="E226" s="10">
         <v>163000</v>
@@ -17163,7 +17163,7 @@
         <v>1405</v>
       </c>
       <c r="D227" s="9">
-        <v>21405</v>
+        <v>1405</v>
       </c>
       <c r="E227" s="10">
         <v>163000</v>
@@ -17192,7 +17192,7 @@
         <v>1406</v>
       </c>
       <c r="D228" s="9">
-        <v>21406</v>
+        <v>1406</v>
       </c>
       <c r="E228" s="10">
         <v>163000</v>
@@ -17221,7 +17221,7 @@
         <v>1407</v>
       </c>
       <c r="D229" s="9">
-        <v>21407</v>
+        <v>1407</v>
       </c>
       <c r="E229" s="10">
         <v>163000</v>
@@ -17250,7 +17250,7 @@
         <v>1408</v>
       </c>
       <c r="D230" s="9">
-        <v>21408</v>
+        <v>1408</v>
       </c>
       <c r="E230" s="10">
         <v>163000</v>
@@ -17279,7 +17279,7 @@
         <v>1501</v>
       </c>
       <c r="D231" s="9">
-        <v>21501</v>
+        <v>1501</v>
       </c>
       <c r="E231" s="10">
         <v>163000</v>
@@ -17308,7 +17308,7 @@
         <v>1502</v>
       </c>
       <c r="D232" s="9">
-        <v>21502</v>
+        <v>1502</v>
       </c>
       <c r="E232" s="10">
         <v>163000</v>
@@ -17337,7 +17337,7 @@
         <v>1503</v>
       </c>
       <c r="D233" s="9">
-        <v>21503</v>
+        <v>1503</v>
       </c>
       <c r="E233" s="10">
         <v>163000</v>
@@ -17366,7 +17366,7 @@
         <v>1504</v>
       </c>
       <c r="D234" s="9">
-        <v>21504</v>
+        <v>1504</v>
       </c>
       <c r="E234" s="10">
         <v>163000</v>
@@ -17395,7 +17395,7 @@
         <v>1505</v>
       </c>
       <c r="D235" s="9">
-        <v>21505</v>
+        <v>1505</v>
       </c>
       <c r="E235" s="10">
         <v>163000</v>
@@ -17424,7 +17424,7 @@
         <v>1506</v>
       </c>
       <c r="D236" s="9">
-        <v>21506</v>
+        <v>1506</v>
       </c>
       <c r="E236" s="10">
         <v>163000</v>
@@ -17453,7 +17453,7 @@
         <v>1507</v>
       </c>
       <c r="D237" s="9">
-        <v>21507</v>
+        <v>1507</v>
       </c>
       <c r="E237" s="10">
         <v>163000</v>
@@ -17482,7 +17482,7 @@
         <v>1508</v>
       </c>
       <c r="D238" s="9">
-        <v>21508</v>
+        <v>1508</v>
       </c>
       <c r="E238" s="10">
         <v>163000</v>
@@ -17511,7 +17511,7 @@
         <v>1</v>
       </c>
       <c r="D239" s="9">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="E239" s="10">
         <v>163000</v>
@@ -17540,7 +17540,7 @@
         <v>8</v>
       </c>
       <c r="D240" s="9">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="E240" s="10">
         <v>152000</v>
@@ -17569,7 +17569,7 @@
         <v>101</v>
       </c>
       <c r="D241" s="9">
-        <v>3101</v>
+        <v>101</v>
       </c>
       <c r="E241" s="10">
         <v>163000</v>
@@ -17598,7 +17598,7 @@
         <v>107</v>
       </c>
       <c r="D242" s="9">
-        <v>3107</v>
+        <v>107</v>
       </c>
       <c r="E242" s="10">
         <v>163000</v>
@@ -17627,7 +17627,7 @@
         <v>108</v>
       </c>
       <c r="D243" s="9">
-        <v>3108</v>
+        <v>108</v>
       </c>
       <c r="E243" s="10">
         <v>163000</v>
@@ -17656,7 +17656,7 @@
         <v>201</v>
       </c>
       <c r="D244" s="9">
-        <v>3201</v>
+        <v>201</v>
       </c>
       <c r="E244" s="10">
         <v>163000</v>
@@ -17685,7 +17685,7 @@
         <v>202</v>
       </c>
       <c r="D245" s="9">
-        <v>3202</v>
+        <v>202</v>
       </c>
       <c r="E245" s="10">
         <v>163000</v>
@@ -17714,7 +17714,7 @@
         <v>203</v>
       </c>
       <c r="D246" s="9">
-        <v>3203</v>
+        <v>203</v>
       </c>
       <c r="E246" s="10">
         <v>152000</v>
@@ -17743,7 +17743,7 @@
         <v>204</v>
       </c>
       <c r="D247" s="9">
-        <v>3204</v>
+        <v>204</v>
       </c>
       <c r="E247" s="10">
         <v>163000</v>
@@ -17772,7 +17772,7 @@
         <v>205</v>
       </c>
       <c r="D248" s="9">
-        <v>3205</v>
+        <v>205</v>
       </c>
       <c r="E248" s="10">
         <v>163000</v>
@@ -17801,7 +17801,7 @@
         <v>206</v>
       </c>
       <c r="D249" s="9">
-        <v>3206</v>
+        <v>206</v>
       </c>
       <c r="E249" s="10">
         <v>152000</v>
@@ -17830,7 +17830,7 @@
         <v>207</v>
       </c>
       <c r="D250" s="9">
-        <v>3207</v>
+        <v>207</v>
       </c>
       <c r="E250" s="10">
         <v>163000</v>
@@ -17859,7 +17859,7 @@
         <v>208</v>
       </c>
       <c r="D251" s="9">
-        <v>3208</v>
+        <v>208</v>
       </c>
       <c r="E251" s="10">
         <v>163000</v>
@@ -17888,7 +17888,7 @@
         <v>301</v>
       </c>
       <c r="D252" s="9">
-        <v>3301</v>
+        <v>301</v>
       </c>
       <c r="E252" s="10">
         <v>163000</v>
@@ -17917,7 +17917,7 @@
         <v>302</v>
       </c>
       <c r="D253" s="9">
-        <v>3302</v>
+        <v>302</v>
       </c>
       <c r="E253" s="10">
         <v>163000</v>
@@ -17946,7 +17946,7 @@
         <v>303</v>
       </c>
       <c r="D254" s="9">
-        <v>3303</v>
+        <v>303</v>
       </c>
       <c r="E254" s="10">
         <v>163000</v>
@@ -17975,7 +17975,7 @@
         <v>304</v>
       </c>
       <c r="D255" s="9">
-        <v>3304</v>
+        <v>304</v>
       </c>
       <c r="E255" s="10">
         <v>163000</v>
@@ -18004,7 +18004,7 @@
         <v>305</v>
       </c>
       <c r="D256" s="9">
-        <v>3305</v>
+        <v>305</v>
       </c>
       <c r="E256" s="10">
         <v>163000</v>
@@ -18033,7 +18033,7 @@
         <v>306</v>
       </c>
       <c r="D257" s="9">
-        <v>3306</v>
+        <v>306</v>
       </c>
       <c r="E257" s="10">
         <v>163000</v>
@@ -18062,7 +18062,7 @@
         <v>307</v>
       </c>
       <c r="D258" s="9">
-        <v>3307</v>
+        <v>307</v>
       </c>
       <c r="E258" s="10">
         <v>163000</v>
@@ -18091,7 +18091,7 @@
         <v>308</v>
       </c>
       <c r="D259" s="9">
-        <v>3308</v>
+        <v>308</v>
       </c>
       <c r="E259" s="10">
         <v>163000</v>
@@ -18120,7 +18120,7 @@
         <v>401</v>
       </c>
       <c r="D260" s="9">
-        <v>3401</v>
+        <v>401</v>
       </c>
       <c r="E260" s="10">
         <v>163000</v>
@@ -18149,7 +18149,7 @@
         <v>402</v>
       </c>
       <c r="D261" s="9">
-        <v>3402</v>
+        <v>402</v>
       </c>
       <c r="E261" s="10">
         <v>163000</v>
@@ -18178,7 +18178,7 @@
         <v>403</v>
       </c>
       <c r="D262" s="9">
-        <v>3403</v>
+        <v>403</v>
       </c>
       <c r="E262" s="10">
         <v>163000</v>
@@ -18207,7 +18207,7 @@
         <v>404</v>
       </c>
       <c r="D263" s="9">
-        <v>3404</v>
+        <v>404</v>
       </c>
       <c r="E263" s="10">
         <v>163000</v>
@@ -18236,7 +18236,7 @@
         <v>405</v>
       </c>
       <c r="D264" s="9">
-        <v>3405</v>
+        <v>405</v>
       </c>
       <c r="E264" s="10">
         <v>163000</v>
@@ -18265,7 +18265,7 @@
         <v>406</v>
       </c>
       <c r="D265" s="9">
-        <v>3406</v>
+        <v>406</v>
       </c>
       <c r="E265" s="10">
         <v>163000</v>
@@ -18294,7 +18294,7 @@
         <v>407</v>
       </c>
       <c r="D266" s="9">
-        <v>3407</v>
+        <v>407</v>
       </c>
       <c r="E266" s="10">
         <v>163000</v>
@@ -18323,7 +18323,7 @@
         <v>408</v>
       </c>
       <c r="D267" s="9">
-        <v>3408</v>
+        <v>408</v>
       </c>
       <c r="E267" s="10">
         <v>163000</v>
@@ -18352,7 +18352,7 @@
         <v>501</v>
       </c>
       <c r="D268" s="9">
-        <v>3501</v>
+        <v>501</v>
       </c>
       <c r="E268" s="10">
         <v>163000</v>
@@ -18381,7 +18381,7 @@
         <v>502</v>
       </c>
       <c r="D269" s="9">
-        <v>3502</v>
+        <v>502</v>
       </c>
       <c r="E269" s="10">
         <v>163000</v>
@@ -18410,7 +18410,7 @@
         <v>503</v>
       </c>
       <c r="D270" s="9">
-        <v>3503</v>
+        <v>503</v>
       </c>
       <c r="E270" s="10">
         <v>163000</v>
@@ -18439,7 +18439,7 @@
         <v>504</v>
       </c>
       <c r="D271" s="9">
-        <v>3504</v>
+        <v>504</v>
       </c>
       <c r="E271" s="10">
         <v>163000</v>
@@ -18468,7 +18468,7 @@
         <v>505</v>
       </c>
       <c r="D272" s="9">
-        <v>3505</v>
+        <v>505</v>
       </c>
       <c r="E272" s="10">
         <v>163000</v>
@@ -18497,7 +18497,7 @@
         <v>506</v>
       </c>
       <c r="D273" s="9">
-        <v>3506</v>
+        <v>506</v>
       </c>
       <c r="E273" s="10">
         <v>163000</v>
@@ -18526,7 +18526,7 @@
         <v>507</v>
       </c>
       <c r="D274" s="9">
-        <v>3507</v>
+        <v>507</v>
       </c>
       <c r="E274" s="10">
         <v>163000</v>
@@ -18555,7 +18555,7 @@
         <v>508</v>
       </c>
       <c r="D275" s="9">
-        <v>3508</v>
+        <v>508</v>
       </c>
       <c r="E275" s="10">
         <v>163000</v>
@@ -18584,7 +18584,7 @@
         <v>601</v>
       </c>
       <c r="D276" s="9">
-        <v>3601</v>
+        <v>601</v>
       </c>
       <c r="E276" s="10">
         <v>163000</v>
@@ -18613,7 +18613,7 @@
         <v>602</v>
       </c>
       <c r="D277" s="9">
-        <v>3602</v>
+        <v>602</v>
       </c>
       <c r="E277" s="10">
         <v>163000</v>
@@ -18642,7 +18642,7 @@
         <v>603</v>
       </c>
       <c r="D278" s="9">
-        <v>3603</v>
+        <v>603</v>
       </c>
       <c r="E278" s="10">
         <v>163000</v>
@@ -18671,7 +18671,7 @@
         <v>604</v>
       </c>
       <c r="D279" s="9">
-        <v>3604</v>
+        <v>604</v>
       </c>
       <c r="E279" s="10">
         <v>163000</v>
@@ -18700,7 +18700,7 @@
         <v>605</v>
       </c>
       <c r="D280" s="9">
-        <v>3605</v>
+        <v>605</v>
       </c>
       <c r="E280" s="10">
         <v>163000</v>
@@ -18729,7 +18729,7 @@
         <v>606</v>
       </c>
       <c r="D281" s="9">
-        <v>3606</v>
+        <v>606</v>
       </c>
       <c r="E281" s="10">
         <v>163000</v>
@@ -18758,7 +18758,7 @@
         <v>607</v>
       </c>
       <c r="D282" s="9">
-        <v>3607</v>
+        <v>607</v>
       </c>
       <c r="E282" s="10">
         <v>163000</v>
@@ -18787,7 +18787,7 @@
         <v>608</v>
       </c>
       <c r="D283" s="9">
-        <v>3608</v>
+        <v>608</v>
       </c>
       <c r="E283" s="10">
         <v>163000</v>
@@ -18816,7 +18816,7 @@
         <v>701</v>
       </c>
       <c r="D284" s="9">
-        <v>3701</v>
+        <v>701</v>
       </c>
       <c r="E284" s="10">
         <v>163000</v>
@@ -18845,7 +18845,7 @@
         <v>702</v>
       </c>
       <c r="D285" s="9">
-        <v>3702</v>
+        <v>702</v>
       </c>
       <c r="E285" s="10">
         <v>163000</v>
@@ -18874,7 +18874,7 @@
         <v>703</v>
       </c>
       <c r="D286" s="9">
-        <v>3703</v>
+        <v>703</v>
       </c>
       <c r="E286" s="10">
         <v>163000</v>
@@ -18903,7 +18903,7 @@
         <v>704</v>
       </c>
       <c r="D287" s="9">
-        <v>3704</v>
+        <v>704</v>
       </c>
       <c r="E287" s="10">
         <v>163000</v>
@@ -18932,7 +18932,7 @@
         <v>705</v>
       </c>
       <c r="D288" s="9">
-        <v>3705</v>
+        <v>705</v>
       </c>
       <c r="E288" s="10">
         <v>163000</v>
@@ -18961,7 +18961,7 @@
         <v>706</v>
       </c>
       <c r="D289" s="9">
-        <v>3706</v>
+        <v>706</v>
       </c>
       <c r="E289" s="10">
         <v>163000</v>
@@ -18990,7 +18990,7 @@
         <v>707</v>
       </c>
       <c r="D290" s="9">
-        <v>3707</v>
+        <v>707</v>
       </c>
       <c r="E290" s="10">
         <v>163000</v>
@@ -19019,7 +19019,7 @@
         <v>708</v>
       </c>
       <c r="D291" s="9">
-        <v>3708</v>
+        <v>708</v>
       </c>
       <c r="E291" s="10">
         <v>163000</v>
@@ -19048,7 +19048,7 @@
         <v>801</v>
       </c>
       <c r="D292" s="9">
-        <v>3801</v>
+        <v>801</v>
       </c>
       <c r="E292" s="10">
         <v>163000</v>
@@ -19077,7 +19077,7 @@
         <v>802</v>
       </c>
       <c r="D293" s="9">
-        <v>3802</v>
+        <v>802</v>
       </c>
       <c r="E293" s="10">
         <v>163000</v>
@@ -19106,7 +19106,7 @@
         <v>803</v>
       </c>
       <c r="D294" s="9">
-        <v>3803</v>
+        <v>803</v>
       </c>
       <c r="E294" s="10">
         <v>163000</v>
@@ -19135,7 +19135,7 @@
         <v>804</v>
       </c>
       <c r="D295" s="9">
-        <v>3804</v>
+        <v>804</v>
       </c>
       <c r="E295" s="10">
         <v>163000</v>
@@ -19164,7 +19164,7 @@
         <v>805</v>
       </c>
       <c r="D296" s="9">
-        <v>3805</v>
+        <v>805</v>
       </c>
       <c r="E296" s="10">
         <v>163000</v>
@@ -19193,7 +19193,7 @@
         <v>806</v>
       </c>
       <c r="D297" s="9">
-        <v>3806</v>
+        <v>806</v>
       </c>
       <c r="E297" s="10">
         <v>163000</v>
@@ -19222,7 +19222,7 @@
         <v>807</v>
       </c>
       <c r="D298" s="9">
-        <v>3807</v>
+        <v>807</v>
       </c>
       <c r="E298" s="10">
         <v>163000</v>
@@ -19251,7 +19251,7 @@
         <v>808</v>
       </c>
       <c r="D299" s="9">
-        <v>3808</v>
+        <v>808</v>
       </c>
       <c r="E299" s="10">
         <v>163000</v>
@@ -19280,7 +19280,7 @@
         <v>901</v>
       </c>
       <c r="D300" s="9">
-        <v>3901</v>
+        <v>901</v>
       </c>
       <c r="E300" s="10">
         <v>163000</v>
@@ -19309,7 +19309,7 @@
         <v>902</v>
       </c>
       <c r="D301" s="9">
-        <v>3902</v>
+        <v>902</v>
       </c>
       <c r="E301" s="10">
         <v>163000</v>
@@ -19338,7 +19338,7 @@
         <v>903</v>
       </c>
       <c r="D302" s="9">
-        <v>3903</v>
+        <v>903</v>
       </c>
       <c r="E302" s="10">
         <v>163000</v>
@@ -19367,7 +19367,7 @@
         <v>904</v>
       </c>
       <c r="D303" s="9">
-        <v>3904</v>
+        <v>904</v>
       </c>
       <c r="E303" s="10">
         <v>163000</v>
@@ -19396,7 +19396,7 @@
         <v>905</v>
       </c>
       <c r="D304" s="9">
-        <v>3905</v>
+        <v>905</v>
       </c>
       <c r="E304" s="10">
         <v>163000</v>
@@ -19425,7 +19425,7 @@
         <v>906</v>
       </c>
       <c r="D305" s="9">
-        <v>3906</v>
+        <v>906</v>
       </c>
       <c r="E305" s="10">
         <v>163000</v>
@@ -19454,7 +19454,7 @@
         <v>907</v>
       </c>
       <c r="D306" s="9">
-        <v>3907</v>
+        <v>907</v>
       </c>
       <c r="E306" s="10">
         <v>163000</v>
@@ -19483,7 +19483,7 @@
         <v>908</v>
       </c>
       <c r="D307" s="9">
-        <v>3908</v>
+        <v>908</v>
       </c>
       <c r="E307" s="10">
         <v>163000</v>
@@ -19512,7 +19512,7 @@
         <v>1001</v>
       </c>
       <c r="D308" s="9">
-        <v>31001</v>
+        <v>1001</v>
       </c>
       <c r="E308" s="10">
         <v>163000</v>
@@ -19541,7 +19541,7 @@
         <v>1002</v>
       </c>
       <c r="D309" s="9">
-        <v>31002</v>
+        <v>1002</v>
       </c>
       <c r="E309" s="10">
         <v>163000</v>
@@ -19570,7 +19570,7 @@
         <v>1003</v>
       </c>
       <c r="D310" s="9">
-        <v>31003</v>
+        <v>1003</v>
       </c>
       <c r="E310" s="10">
         <v>163000</v>
@@ -19599,7 +19599,7 @@
         <v>1004</v>
       </c>
       <c r="D311" s="9">
-        <v>31004</v>
+        <v>1004</v>
       </c>
       <c r="E311" s="10">
         <v>163000</v>
@@ -19628,7 +19628,7 @@
         <v>1005</v>
       </c>
       <c r="D312" s="9">
-        <v>31005</v>
+        <v>1005</v>
       </c>
       <c r="E312" s="10">
         <v>163000</v>
@@ -19657,7 +19657,7 @@
         <v>1006</v>
       </c>
       <c r="D313" s="9">
-        <v>31006</v>
+        <v>1006</v>
       </c>
       <c r="E313" s="10">
         <v>163000</v>
@@ -19686,7 +19686,7 @@
         <v>1007</v>
       </c>
       <c r="D314" s="9">
-        <v>31007</v>
+        <v>1007</v>
       </c>
       <c r="E314" s="10">
         <v>163000</v>
@@ -19715,7 +19715,7 @@
         <v>1008</v>
       </c>
       <c r="D315" s="9">
-        <v>31008</v>
+        <v>1008</v>
       </c>
       <c r="E315" s="10">
         <v>163000</v>
@@ -19744,7 +19744,7 @@
         <v>1101</v>
       </c>
       <c r="D316" s="9">
-        <v>31101</v>
+        <v>1101</v>
       </c>
       <c r="E316" s="10">
         <v>163000</v>
@@ -19773,7 +19773,7 @@
         <v>1102</v>
       </c>
       <c r="D317" s="9">
-        <v>31102</v>
+        <v>1102</v>
       </c>
       <c r="E317" s="10">
         <v>163000</v>
@@ -19802,7 +19802,7 @@
         <v>1103</v>
       </c>
       <c r="D318" s="9">
-        <v>31103</v>
+        <v>1103</v>
       </c>
       <c r="E318" s="10">
         <v>163000</v>
@@ -19831,7 +19831,7 @@
         <v>1104</v>
       </c>
       <c r="D319" s="9">
-        <v>31104</v>
+        <v>1104</v>
       </c>
       <c r="E319" s="10">
         <v>163000</v>
@@ -19860,7 +19860,7 @@
         <v>1105</v>
       </c>
       <c r="D320" s="9">
-        <v>31105</v>
+        <v>1105</v>
       </c>
       <c r="E320" s="10">
         <v>163000</v>
@@ -19889,7 +19889,7 @@
         <v>1106</v>
       </c>
       <c r="D321" s="9">
-        <v>31106</v>
+        <v>1106</v>
       </c>
       <c r="E321" s="10">
         <v>163000</v>
@@ -19918,7 +19918,7 @@
         <v>1107</v>
       </c>
       <c r="D322" s="9">
-        <v>31107</v>
+        <v>1107</v>
       </c>
       <c r="E322" s="10">
         <v>163000</v>
@@ -19947,7 +19947,7 @@
         <v>1108</v>
       </c>
       <c r="D323" s="9">
-        <v>31108</v>
+        <v>1108</v>
       </c>
       <c r="E323" s="10">
         <v>163000</v>
@@ -19976,7 +19976,7 @@
         <v>1201</v>
       </c>
       <c r="D324" s="9">
-        <v>31201</v>
+        <v>1201</v>
       </c>
       <c r="E324" s="10">
         <v>163000</v>
@@ -20005,7 +20005,7 @@
         <v>1202</v>
       </c>
       <c r="D325" s="9">
-        <v>31202</v>
+        <v>1202</v>
       </c>
       <c r="E325" s="10">
         <v>163000</v>
@@ -20034,7 +20034,7 @@
         <v>1203</v>
       </c>
       <c r="D326" s="9">
-        <v>31203</v>
+        <v>1203</v>
       </c>
       <c r="E326" s="10">
         <v>163000</v>
@@ -20063,7 +20063,7 @@
         <v>1204</v>
       </c>
       <c r="D327" s="9">
-        <v>31204</v>
+        <v>1204</v>
       </c>
       <c r="E327" s="10">
         <v>163000</v>
@@ -20092,7 +20092,7 @@
         <v>1205</v>
       </c>
       <c r="D328" s="9">
-        <v>31205</v>
+        <v>1205</v>
       </c>
       <c r="E328" s="10">
         <v>163000</v>
@@ -20121,7 +20121,7 @@
         <v>1206</v>
       </c>
       <c r="D329" s="9">
-        <v>31206</v>
+        <v>1206</v>
       </c>
       <c r="E329" s="10">
         <v>163000</v>
@@ -20150,7 +20150,7 @@
         <v>1207</v>
       </c>
       <c r="D330" s="9">
-        <v>31207</v>
+        <v>1207</v>
       </c>
       <c r="E330" s="10">
         <v>163000</v>
@@ -20179,7 +20179,7 @@
         <v>1208</v>
       </c>
       <c r="D331" s="9">
-        <v>31208</v>
+        <v>1208</v>
       </c>
       <c r="E331" s="10">
         <v>163000</v>
@@ -20208,7 +20208,7 @@
         <v>1301</v>
       </c>
       <c r="D332" s="9">
-        <v>31301</v>
+        <v>1301</v>
       </c>
       <c r="E332" s="10">
         <v>163000</v>
@@ -20237,7 +20237,7 @@
         <v>1302</v>
       </c>
       <c r="D333" s="9">
-        <v>31302</v>
+        <v>1302</v>
       </c>
       <c r="E333" s="10">
         <v>163000</v>
@@ -20266,7 +20266,7 @@
         <v>1303</v>
       </c>
       <c r="D334" s="9">
-        <v>31303</v>
+        <v>1303</v>
       </c>
       <c r="E334" s="10">
         <v>163000</v>
@@ -20295,7 +20295,7 @@
         <v>1304</v>
       </c>
       <c r="D335" s="9">
-        <v>31304</v>
+        <v>1304</v>
       </c>
       <c r="E335" s="10">
         <v>163000</v>
@@ -20324,7 +20324,7 @@
         <v>1305</v>
       </c>
       <c r="D336" s="9">
-        <v>31305</v>
+        <v>1305</v>
       </c>
       <c r="E336" s="10">
         <v>163000</v>
@@ -20353,7 +20353,7 @@
         <v>1306</v>
       </c>
       <c r="D337" s="9">
-        <v>31306</v>
+        <v>1306</v>
       </c>
       <c r="E337" s="10">
         <v>163000</v>
@@ -20382,7 +20382,7 @@
         <v>1307</v>
       </c>
       <c r="D338" s="9">
-        <v>31307</v>
+        <v>1307</v>
       </c>
       <c r="E338" s="10">
         <v>163000</v>
@@ -20411,7 +20411,7 @@
         <v>1308</v>
       </c>
       <c r="D339" s="9">
-        <v>31308</v>
+        <v>1308</v>
       </c>
       <c r="E339" s="10">
         <v>163000</v>
@@ -20440,7 +20440,7 @@
         <v>1401</v>
       </c>
       <c r="D340" s="9">
-        <v>31401</v>
+        <v>1401</v>
       </c>
       <c r="E340" s="10">
         <v>163000</v>
@@ -20469,7 +20469,7 @@
         <v>1402</v>
       </c>
       <c r="D341" s="9">
-        <v>31402</v>
+        <v>1402</v>
       </c>
       <c r="E341" s="10">
         <v>163000</v>
@@ -20498,7 +20498,7 @@
         <v>1403</v>
       </c>
       <c r="D342" s="9">
-        <v>31403</v>
+        <v>1403</v>
       </c>
       <c r="E342" s="10">
         <v>163000</v>
@@ -20527,7 +20527,7 @@
         <v>1404</v>
       </c>
       <c r="D343" s="9">
-        <v>31404</v>
+        <v>1404</v>
       </c>
       <c r="E343" s="10">
         <v>163000</v>
@@ -20556,7 +20556,7 @@
         <v>1405</v>
       </c>
       <c r="D344" s="9">
-        <v>31405</v>
+        <v>1405</v>
       </c>
       <c r="E344" s="10">
         <v>163000</v>
@@ -20585,7 +20585,7 @@
         <v>1406</v>
       </c>
       <c r="D345" s="9">
-        <v>31406</v>
+        <v>1406</v>
       </c>
       <c r="E345" s="10">
         <v>163000</v>
@@ -20614,7 +20614,7 @@
         <v>1407</v>
       </c>
       <c r="D346" s="9">
-        <v>31407</v>
+        <v>1407</v>
       </c>
       <c r="E346" s="10">
         <v>163000</v>
@@ -20643,7 +20643,7 @@
         <v>1408</v>
       </c>
       <c r="D347" s="9">
-        <v>31408</v>
+        <v>1408</v>
       </c>
       <c r="E347" s="10">
         <v>163000</v>
@@ -20672,7 +20672,7 @@
         <v>1501</v>
       </c>
       <c r="D348" s="9">
-        <v>31501</v>
+        <v>1501</v>
       </c>
       <c r="E348" s="10">
         <v>163000</v>
@@ -20701,7 +20701,7 @@
         <v>1502</v>
       </c>
       <c r="D349" s="9">
-        <v>31502</v>
+        <v>1502</v>
       </c>
       <c r="E349" s="10">
         <v>163000</v>
@@ -20730,7 +20730,7 @@
         <v>1503</v>
       </c>
       <c r="D350" s="9">
-        <v>31503</v>
+        <v>1503</v>
       </c>
       <c r="E350" s="10">
         <v>163000</v>
@@ -20759,7 +20759,7 @@
         <v>1504</v>
       </c>
       <c r="D351" s="9">
-        <v>31504</v>
+        <v>1504</v>
       </c>
       <c r="E351" s="10">
         <v>163000</v>
@@ -20788,7 +20788,7 @@
         <v>1505</v>
       </c>
       <c r="D352" s="9">
-        <v>31505</v>
+        <v>1505</v>
       </c>
       <c r="E352" s="10">
         <v>163000</v>
@@ -20817,7 +20817,7 @@
         <v>1506</v>
       </c>
       <c r="D353" s="9">
-        <v>31506</v>
+        <v>1506</v>
       </c>
       <c r="E353" s="10">
         <v>163000</v>
@@ -20846,7 +20846,7 @@
         <v>1507</v>
       </c>
       <c r="D354" s="9">
-        <v>31507</v>
+        <v>1507</v>
       </c>
       <c r="E354" s="10">
         <v>163000</v>
@@ -20875,7 +20875,7 @@
         <v>1508</v>
       </c>
       <c r="D355" s="9">
-        <v>31508</v>
+        <v>1508</v>
       </c>
       <c r="E355" s="10">
         <v>163000</v>
@@ -20904,7 +20904,7 @@
         <v>101</v>
       </c>
       <c r="D356" s="9">
-        <v>4101</v>
+        <v>101</v>
       </c>
       <c r="E356" s="10">
         <v>164000</v>
@@ -20933,7 +20933,7 @@
         <v>108</v>
       </c>
       <c r="D357" s="9">
-        <v>4108</v>
+        <v>108</v>
       </c>
       <c r="E357" s="10">
         <v>164000</v>
@@ -20962,7 +20962,7 @@
         <v>201</v>
       </c>
       <c r="D358" s="9">
-        <v>4201</v>
+        <v>201</v>
       </c>
       <c r="E358" s="10">
         <v>164000</v>
@@ -20991,7 +20991,7 @@
         <v>202</v>
       </c>
       <c r="D359" s="9">
-        <v>4202</v>
+        <v>202</v>
       </c>
       <c r="E359" s="10">
         <v>164000</v>
@@ -21020,7 +21020,7 @@
         <v>206</v>
       </c>
       <c r="D360" s="9">
-        <v>4206</v>
+        <v>206</v>
       </c>
       <c r="E360" s="10">
         <v>153000</v>
@@ -21049,7 +21049,7 @@
         <v>207</v>
       </c>
       <c r="D361" s="9">
-        <v>4207</v>
+        <v>207</v>
       </c>
       <c r="E361" s="10">
         <v>164000</v>
@@ -21078,7 +21078,7 @@
         <v>208</v>
       </c>
       <c r="D362" s="9">
-        <v>4208</v>
+        <v>208</v>
       </c>
       <c r="E362" s="10">
         <v>164000</v>
@@ -21107,7 +21107,7 @@
         <v>301</v>
       </c>
       <c r="D363" s="9">
-        <v>4301</v>
+        <v>301</v>
       </c>
       <c r="E363" s="10">
         <v>164000</v>
@@ -21136,7 +21136,7 @@
         <v>302</v>
       </c>
       <c r="D364" s="9">
-        <v>4302</v>
+        <v>302</v>
       </c>
       <c r="E364" s="10">
         <v>164000</v>
@@ -21165,7 +21165,7 @@
         <v>303</v>
       </c>
       <c r="D365" s="9">
-        <v>4303</v>
+        <v>303</v>
       </c>
       <c r="E365" s="10">
         <v>153000</v>
@@ -21194,7 +21194,7 @@
         <v>304</v>
       </c>
       <c r="D366" s="9">
-        <v>4304</v>
+        <v>304</v>
       </c>
       <c r="E366" s="10">
         <v>164000</v>
@@ -21223,7 +21223,7 @@
         <v>305</v>
       </c>
       <c r="D367" s="9">
-        <v>4305</v>
+        <v>305</v>
       </c>
       <c r="E367" s="10">
         <v>164000</v>
@@ -21252,7 +21252,7 @@
         <v>306</v>
       </c>
       <c r="D368" s="9">
-        <v>4306</v>
+        <v>306</v>
       </c>
       <c r="E368" s="10">
         <v>164000</v>
@@ -21281,7 +21281,7 @@
         <v>307</v>
       </c>
       <c r="D369" s="9">
-        <v>4307</v>
+        <v>307</v>
       </c>
       <c r="E369" s="10">
         <v>164000</v>
@@ -21310,7 +21310,7 @@
         <v>308</v>
       </c>
       <c r="D370" s="9">
-        <v>4308</v>
+        <v>308</v>
       </c>
       <c r="E370" s="10">
         <v>164000</v>
@@ -21339,7 +21339,7 @@
         <v>401</v>
       </c>
       <c r="D371" s="9">
-        <v>4401</v>
+        <v>401</v>
       </c>
       <c r="E371" s="10">
         <v>164000</v>
@@ -21368,7 +21368,7 @@
         <v>402</v>
       </c>
       <c r="D372" s="9">
-        <v>4402</v>
+        <v>402</v>
       </c>
       <c r="E372" s="10">
         <v>164000</v>
@@ -21397,7 +21397,7 @@
         <v>403</v>
       </c>
       <c r="D373" s="9">
-        <v>4403</v>
+        <v>403</v>
       </c>
       <c r="E373" s="10">
         <v>164000</v>
@@ -21426,7 +21426,7 @@
         <v>404</v>
       </c>
       <c r="D374" s="9">
-        <v>4404</v>
+        <v>404</v>
       </c>
       <c r="E374" s="10">
         <v>164000</v>
@@ -21455,7 +21455,7 @@
         <v>405</v>
       </c>
       <c r="D375" s="9">
-        <v>4405</v>
+        <v>405</v>
       </c>
       <c r="E375" s="10">
         <v>164000</v>
@@ -21484,7 +21484,7 @@
         <v>406</v>
       </c>
       <c r="D376" s="9">
-        <v>4406</v>
+        <v>406</v>
       </c>
       <c r="E376" s="10">
         <v>164000</v>
@@ -21513,7 +21513,7 @@
         <v>407</v>
       </c>
       <c r="D377" s="9">
-        <v>4407</v>
+        <v>407</v>
       </c>
       <c r="E377" s="10">
         <v>164000</v>
@@ -21542,7 +21542,7 @@
         <v>408</v>
       </c>
       <c r="D378" s="9">
-        <v>4408</v>
+        <v>408</v>
       </c>
       <c r="E378" s="10">
         <v>164000</v>
@@ -21571,7 +21571,7 @@
         <v>501</v>
       </c>
       <c r="D379" s="9">
-        <v>4501</v>
+        <v>501</v>
       </c>
       <c r="E379" s="10">
         <v>164000</v>
@@ -21600,7 +21600,7 @@
         <v>502</v>
       </c>
       <c r="D380" s="9">
-        <v>4502</v>
+        <v>502</v>
       </c>
       <c r="E380" s="10">
         <v>164000</v>
@@ -21629,7 +21629,7 @@
         <v>503</v>
       </c>
       <c r="D381" s="9">
-        <v>4503</v>
+        <v>503</v>
       </c>
       <c r="E381" s="10">
         <v>164000</v>
@@ -21658,7 +21658,7 @@
         <v>504</v>
       </c>
       <c r="D382" s="9">
-        <v>4504</v>
+        <v>504</v>
       </c>
       <c r="E382" s="10">
         <v>164000</v>
@@ -21687,7 +21687,7 @@
         <v>505</v>
       </c>
       <c r="D383" s="9">
-        <v>4505</v>
+        <v>505</v>
       </c>
       <c r="E383" s="10">
         <v>164000</v>
@@ -21716,7 +21716,7 @@
         <v>506</v>
       </c>
       <c r="D384" s="9">
-        <v>4506</v>
+        <v>506</v>
       </c>
       <c r="E384" s="10">
         <v>164000</v>
@@ -21745,7 +21745,7 @@
         <v>507</v>
       </c>
       <c r="D385" s="9">
-        <v>4507</v>
+        <v>507</v>
       </c>
       <c r="E385" s="10">
         <v>164000</v>
@@ -21774,7 +21774,7 @@
         <v>508</v>
       </c>
       <c r="D386" s="9">
-        <v>4508</v>
+        <v>508</v>
       </c>
       <c r="E386" s="10">
         <v>164000</v>
@@ -21803,7 +21803,7 @@
         <v>601</v>
       </c>
       <c r="D387" s="9">
-        <v>4601</v>
+        <v>601</v>
       </c>
       <c r="E387" s="10">
         <v>164000</v>
@@ -21832,7 +21832,7 @@
         <v>602</v>
       </c>
       <c r="D388" s="9">
-        <v>4602</v>
+        <v>602</v>
       </c>
       <c r="E388" s="10">
         <v>164000</v>
@@ -21861,7 +21861,7 @@
         <v>603</v>
       </c>
       <c r="D389" s="9">
-        <v>4603</v>
+        <v>603</v>
       </c>
       <c r="E389" s="10">
         <v>164000</v>
@@ -21890,7 +21890,7 @@
         <v>604</v>
       </c>
       <c r="D390" s="9">
-        <v>4604</v>
+        <v>604</v>
       </c>
       <c r="E390" s="10">
         <v>164000</v>
@@ -21919,7 +21919,7 @@
         <v>605</v>
       </c>
       <c r="D391" s="9">
-        <v>4605</v>
+        <v>605</v>
       </c>
       <c r="E391" s="10">
         <v>164000</v>
@@ -21948,7 +21948,7 @@
         <v>606</v>
       </c>
       <c r="D392" s="9">
-        <v>4606</v>
+        <v>606</v>
       </c>
       <c r="E392" s="10">
         <v>164000</v>
@@ -21977,7 +21977,7 @@
         <v>607</v>
       </c>
       <c r="D393" s="9">
-        <v>4607</v>
+        <v>607</v>
       </c>
       <c r="E393" s="10">
         <v>164000</v>
@@ -22006,7 +22006,7 @@
         <v>608</v>
       </c>
       <c r="D394" s="9">
-        <v>4608</v>
+        <v>608</v>
       </c>
       <c r="E394" s="10">
         <v>164000</v>
@@ -22035,7 +22035,7 @@
         <v>701</v>
       </c>
       <c r="D395" s="9">
-        <v>4701</v>
+        <v>701</v>
       </c>
       <c r="E395" s="10">
         <v>164000</v>
@@ -22064,7 +22064,7 @@
         <v>702</v>
       </c>
       <c r="D396" s="9">
-        <v>4702</v>
+        <v>702</v>
       </c>
       <c r="E396" s="10">
         <v>164000</v>
@@ -22093,7 +22093,7 @@
         <v>703</v>
       </c>
       <c r="D397" s="9">
-        <v>4703</v>
+        <v>703</v>
       </c>
       <c r="E397" s="10">
         <v>164000</v>
@@ -22122,7 +22122,7 @@
         <v>704</v>
       </c>
       <c r="D398" s="9">
-        <v>4704</v>
+        <v>704</v>
       </c>
       <c r="E398" s="10">
         <v>164000</v>
@@ -22151,7 +22151,7 @@
         <v>705</v>
       </c>
       <c r="D399" s="9">
-        <v>4705</v>
+        <v>705</v>
       </c>
       <c r="E399" s="10">
         <v>164000</v>
@@ -22180,7 +22180,7 @@
         <v>706</v>
       </c>
       <c r="D400" s="9">
-        <v>4706</v>
+        <v>706</v>
       </c>
       <c r="E400" s="10">
         <v>164000</v>
@@ -22209,7 +22209,7 @@
         <v>707</v>
       </c>
       <c r="D401" s="9">
-        <v>4707</v>
+        <v>707</v>
       </c>
       <c r="E401" s="10">
         <v>164000</v>
@@ -22238,7 +22238,7 @@
         <v>708</v>
       </c>
       <c r="D402" s="9">
-        <v>4708</v>
+        <v>708</v>
       </c>
       <c r="E402" s="10">
         <v>164000</v>
@@ -22267,7 +22267,7 @@
         <v>801</v>
       </c>
       <c r="D403" s="9">
-        <v>4801</v>
+        <v>801</v>
       </c>
       <c r="E403" s="10">
         <v>164000</v>
@@ -22296,7 +22296,7 @@
         <v>802</v>
       </c>
       <c r="D404" s="9">
-        <v>4802</v>
+        <v>802</v>
       </c>
       <c r="E404" s="10">
         <v>164000</v>
@@ -22325,7 +22325,7 @@
         <v>803</v>
       </c>
       <c r="D405" s="9">
-        <v>4803</v>
+        <v>803</v>
       </c>
       <c r="E405" s="10">
         <v>164000</v>
@@ -22354,7 +22354,7 @@
         <v>804</v>
       </c>
       <c r="D406" s="9">
-        <v>4804</v>
+        <v>804</v>
       </c>
       <c r="E406" s="10">
         <v>164000</v>
@@ -22383,7 +22383,7 @@
         <v>805</v>
       </c>
       <c r="D407" s="9">
-        <v>4805</v>
+        <v>805</v>
       </c>
       <c r="E407" s="10">
         <v>164000</v>
@@ -22412,7 +22412,7 @@
         <v>806</v>
       </c>
       <c r="D408" s="9">
-        <v>4806</v>
+        <v>806</v>
       </c>
       <c r="E408" s="10">
         <v>164000</v>
@@ -22441,7 +22441,7 @@
         <v>807</v>
       </c>
       <c r="D409" s="9">
-        <v>4807</v>
+        <v>807</v>
       </c>
       <c r="E409" s="10">
         <v>164000</v>
@@ -22470,7 +22470,7 @@
         <v>808</v>
       </c>
       <c r="D410" s="9">
-        <v>4808</v>
+        <v>808</v>
       </c>
       <c r="E410" s="10">
         <v>164000</v>
@@ -22499,7 +22499,7 @@
         <v>901</v>
       </c>
       <c r="D411" s="9">
-        <v>4901</v>
+        <v>901</v>
       </c>
       <c r="E411" s="10">
         <v>164000</v>
@@ -22528,7 +22528,7 @@
         <v>902</v>
       </c>
       <c r="D412" s="9">
-        <v>4902</v>
+        <v>902</v>
       </c>
       <c r="E412" s="10">
         <v>164000</v>
@@ -22557,7 +22557,7 @@
         <v>903</v>
       </c>
       <c r="D413" s="9">
-        <v>4903</v>
+        <v>903</v>
       </c>
       <c r="E413" s="10">
         <v>164000</v>
@@ -22586,7 +22586,7 @@
         <v>904</v>
       </c>
       <c r="D414" s="9">
-        <v>4904</v>
+        <v>904</v>
       </c>
       <c r="E414" s="10">
         <v>164000</v>
@@ -22615,7 +22615,7 @@
         <v>905</v>
       </c>
       <c r="D415" s="9">
-        <v>4905</v>
+        <v>905</v>
       </c>
       <c r="E415" s="10">
         <v>164000</v>
@@ -22644,7 +22644,7 @@
         <v>906</v>
       </c>
       <c r="D416" s="9">
-        <v>4906</v>
+        <v>906</v>
       </c>
       <c r="E416" s="10">
         <v>164000</v>
@@ -22673,7 +22673,7 @@
         <v>907</v>
       </c>
       <c r="D417" s="9">
-        <v>4907</v>
+        <v>907</v>
       </c>
       <c r="E417" s="10">
         <v>164000</v>
@@ -22702,7 +22702,7 @@
         <v>908</v>
       </c>
       <c r="D418" s="9">
-        <v>4908</v>
+        <v>908</v>
       </c>
       <c r="E418" s="10">
         <v>164000</v>
@@ -22731,7 +22731,7 @@
         <v>1001</v>
       </c>
       <c r="D419" s="9">
-        <v>41001</v>
+        <v>1001</v>
       </c>
       <c r="E419" s="10">
         <v>164000</v>
@@ -22760,7 +22760,7 @@
         <v>1002</v>
       </c>
       <c r="D420" s="9">
-        <v>41002</v>
+        <v>1002</v>
       </c>
       <c r="E420" s="10">
         <v>164000</v>
@@ -22789,7 +22789,7 @@
         <v>1003</v>
       </c>
       <c r="D421" s="9">
-        <v>41003</v>
+        <v>1003</v>
       </c>
       <c r="E421" s="10">
         <v>164000</v>
@@ -22818,7 +22818,7 @@
         <v>1004</v>
       </c>
       <c r="D422" s="9">
-        <v>41004</v>
+        <v>1004</v>
       </c>
       <c r="E422" s="10">
         <v>164000</v>
@@ -22847,7 +22847,7 @@
         <v>1005</v>
       </c>
       <c r="D423" s="9">
-        <v>41005</v>
+        <v>1005</v>
       </c>
       <c r="E423" s="10">
         <v>164000</v>
@@ -22876,7 +22876,7 @@
         <v>1006</v>
       </c>
       <c r="D424" s="9">
-        <v>41006</v>
+        <v>1006</v>
       </c>
       <c r="E424" s="10">
         <v>164000</v>
@@ -22905,7 +22905,7 @@
         <v>1007</v>
       </c>
       <c r="D425" s="9">
-        <v>41007</v>
+        <v>1007</v>
       </c>
       <c r="E425" s="10">
         <v>164000</v>
@@ -22934,7 +22934,7 @@
         <v>1008</v>
       </c>
       <c r="D426" s="9">
-        <v>41008</v>
+        <v>1008</v>
       </c>
       <c r="E426" s="10">
         <v>164000</v>
@@ -22963,7 +22963,7 @@
         <v>1101</v>
       </c>
       <c r="D427" s="9">
-        <v>41101</v>
+        <v>1101</v>
       </c>
       <c r="E427" s="10">
         <v>164000</v>
@@ -22992,7 +22992,7 @@
         <v>1102</v>
       </c>
       <c r="D428" s="9">
-        <v>41102</v>
+        <v>1102</v>
       </c>
       <c r="E428" s="10">
         <v>164000</v>
@@ -23021,7 +23021,7 @@
         <v>1103</v>
       </c>
       <c r="D429" s="9">
-        <v>41103</v>
+        <v>1103</v>
       </c>
       <c r="E429" s="10">
         <v>164000</v>
@@ -23050,7 +23050,7 @@
         <v>1104</v>
       </c>
       <c r="D430" s="9">
-        <v>41104</v>
+        <v>1104</v>
       </c>
       <c r="E430" s="10">
         <v>164000</v>
@@ -23079,7 +23079,7 @@
         <v>1105</v>
       </c>
       <c r="D431" s="9">
-        <v>41105</v>
+        <v>1105</v>
       </c>
       <c r="E431" s="10">
         <v>164000</v>
@@ -23108,7 +23108,7 @@
         <v>1106</v>
       </c>
       <c r="D432" s="9">
-        <v>41106</v>
+        <v>1106</v>
       </c>
       <c r="E432" s="10">
         <v>164000</v>
@@ -23137,7 +23137,7 @@
         <v>1107</v>
       </c>
       <c r="D433" s="9">
-        <v>41107</v>
+        <v>1107</v>
       </c>
       <c r="E433" s="10">
         <v>164000</v>
@@ -23166,7 +23166,7 @@
         <v>1108</v>
       </c>
       <c r="D434" s="9">
-        <v>41108</v>
+        <v>1108</v>
       </c>
       <c r="E434" s="10">
         <v>164000</v>
@@ -23195,7 +23195,7 @@
         <v>1201</v>
       </c>
       <c r="D435" s="9">
-        <v>41201</v>
+        <v>1201</v>
       </c>
       <c r="E435" s="10">
         <v>164000</v>
@@ -23224,7 +23224,7 @@
         <v>1202</v>
       </c>
       <c r="D436" s="9">
-        <v>41202</v>
+        <v>1202</v>
       </c>
       <c r="E436" s="10">
         <v>164000</v>
@@ -23253,7 +23253,7 @@
         <v>1203</v>
       </c>
       <c r="D437" s="9">
-        <v>41203</v>
+        <v>1203</v>
       </c>
       <c r="E437" s="10">
         <v>164000</v>
@@ -23282,7 +23282,7 @@
         <v>1204</v>
       </c>
       <c r="D438" s="9">
-        <v>41204</v>
+        <v>1204</v>
       </c>
       <c r="E438" s="10">
         <v>164000</v>
@@ -23311,7 +23311,7 @@
         <v>1205</v>
       </c>
       <c r="D439" s="9">
-        <v>41205</v>
+        <v>1205</v>
       </c>
       <c r="E439" s="10">
         <v>164000</v>
@@ -23340,7 +23340,7 @@
         <v>1206</v>
       </c>
       <c r="D440" s="9">
-        <v>41206</v>
+        <v>1206</v>
       </c>
       <c r="E440" s="10">
         <v>164000</v>
@@ -23369,7 +23369,7 @@
         <v>1207</v>
       </c>
       <c r="D441" s="9">
-        <v>41207</v>
+        <v>1207</v>
       </c>
       <c r="E441" s="10">
         <v>164000</v>
@@ -23398,7 +23398,7 @@
         <v>1208</v>
       </c>
       <c r="D442" s="9">
-        <v>41208</v>
+        <v>1208</v>
       </c>
       <c r="E442" s="10">
         <v>164000</v>
@@ -23427,7 +23427,7 @@
         <v>1301</v>
       </c>
       <c r="D443" s="9">
-        <v>41301</v>
+        <v>1301</v>
       </c>
       <c r="E443" s="10">
         <v>164000</v>
@@ -23456,7 +23456,7 @@
         <v>1302</v>
       </c>
       <c r="D444" s="9">
-        <v>41302</v>
+        <v>1302</v>
       </c>
       <c r="E444" s="10">
         <v>164000</v>
@@ -23485,7 +23485,7 @@
         <v>1303</v>
       </c>
       <c r="D445" s="9">
-        <v>41303</v>
+        <v>1303</v>
       </c>
       <c r="E445" s="10">
         <v>164000</v>
@@ -23514,7 +23514,7 @@
         <v>1304</v>
       </c>
       <c r="D446" s="9">
-        <v>41304</v>
+        <v>1304</v>
       </c>
       <c r="E446" s="10">
         <v>164000</v>
@@ -23543,7 +23543,7 @@
         <v>1305</v>
       </c>
       <c r="D447" s="9">
-        <v>41305</v>
+        <v>1305</v>
       </c>
       <c r="E447" s="10">
         <v>164000</v>
@@ -23572,7 +23572,7 @@
         <v>1306</v>
       </c>
       <c r="D448" s="9">
-        <v>41306</v>
+        <v>1306</v>
       </c>
       <c r="E448" s="10">
         <v>164000</v>
@@ -23601,7 +23601,7 @@
         <v>1307</v>
       </c>
       <c r="D449" s="9">
-        <v>41307</v>
+        <v>1307</v>
       </c>
       <c r="E449" s="10">
         <v>164000</v>
@@ -23630,7 +23630,7 @@
         <v>1308</v>
       </c>
       <c r="D450" s="9">
-        <v>41308</v>
+        <v>1308</v>
       </c>
       <c r="E450" s="10">
         <v>164000</v>
@@ -23659,7 +23659,7 @@
         <v>1401</v>
       </c>
       <c r="D451" s="9">
-        <v>41401</v>
+        <v>1401</v>
       </c>
       <c r="E451" s="10">
         <v>164000</v>
@@ -23688,7 +23688,7 @@
         <v>1402</v>
       </c>
       <c r="D452" s="9">
-        <v>41402</v>
+        <v>1402</v>
       </c>
       <c r="E452" s="10">
         <v>164000</v>
@@ -23717,7 +23717,7 @@
         <v>1403</v>
       </c>
       <c r="D453" s="9">
-        <v>41403</v>
+        <v>1403</v>
       </c>
       <c r="E453" s="10">
         <v>164000</v>
@@ -23746,7 +23746,7 @@
         <v>1404</v>
       </c>
       <c r="D454" s="9">
-        <v>41404</v>
+        <v>1404</v>
       </c>
       <c r="E454" s="10">
         <v>164000</v>
@@ -23775,7 +23775,7 @@
         <v>1405</v>
       </c>
       <c r="D455" s="9">
-        <v>41405</v>
+        <v>1405</v>
       </c>
       <c r="E455" s="10">
         <v>164000</v>
@@ -23804,7 +23804,7 @@
         <v>1406</v>
       </c>
       <c r="D456" s="9">
-        <v>41406</v>
+        <v>1406</v>
       </c>
       <c r="E456" s="10">
         <v>164000</v>
@@ -23833,7 +23833,7 @@
         <v>1406</v>
       </c>
       <c r="D457" s="9">
-        <v>41406</v>
+        <v>1406</v>
       </c>
       <c r="E457" s="10">
         <v>164000</v>
@@ -23862,7 +23862,7 @@
         <v>1408</v>
       </c>
       <c r="D458" s="9">
-        <v>41408</v>
+        <v>1408</v>
       </c>
       <c r="E458" s="10">
         <v>164000</v>
@@ -23891,7 +23891,7 @@
         <v>1501</v>
       </c>
       <c r="D459" s="9">
-        <v>41501</v>
+        <v>1501</v>
       </c>
       <c r="E459" s="10">
         <v>164000</v>
@@ -23920,7 +23920,7 @@
         <v>1502</v>
       </c>
       <c r="D460" s="9">
-        <v>41502</v>
+        <v>1502</v>
       </c>
       <c r="E460" s="10">
         <v>164000</v>
@@ -23949,7 +23949,7 @@
         <v>1503</v>
       </c>
       <c r="D461" s="9">
-        <v>41503</v>
+        <v>1503</v>
       </c>
       <c r="E461" s="10">
         <v>164000</v>
@@ -23978,7 +23978,7 @@
         <v>1504</v>
       </c>
       <c r="D462" s="9">
-        <v>41504</v>
+        <v>1504</v>
       </c>
       <c r="E462" s="10">
         <v>164000</v>
@@ -24007,7 +24007,7 @@
         <v>1505</v>
       </c>
       <c r="D463" s="9">
-        <v>41505</v>
+        <v>1505</v>
       </c>
       <c r="E463" s="10">
         <v>164000</v>
@@ -24036,7 +24036,7 @@
         <v>1506</v>
       </c>
       <c r="D464" s="9">
-        <v>41506</v>
+        <v>1506</v>
       </c>
       <c r="E464" s="10">
         <v>164000</v>
@@ -24065,7 +24065,7 @@
         <v>1507</v>
       </c>
       <c r="D465" s="9">
-        <v>41507</v>
+        <v>1507</v>
       </c>
       <c r="E465" s="10">
         <v>164000</v>
@@ -24094,7 +24094,7 @@
         <v>1508</v>
       </c>
       <c r="D466" s="9">
-        <v>41508</v>
+        <v>1508</v>
       </c>
       <c r="E466" s="10">
         <v>164000</v>
@@ -24123,7 +24123,7 @@
         <v>104</v>
       </c>
       <c r="D467" s="9">
-        <v>5104</v>
+        <v>104</v>
       </c>
       <c r="E467" s="10">
         <v>165000</v>
@@ -24152,7 +24152,7 @@
         <v>105</v>
       </c>
       <c r="D468" s="9">
-        <v>5105</v>
+        <v>105</v>
       </c>
       <c r="E468" s="10">
         <v>165000</v>
@@ -24181,7 +24181,7 @@
         <v>202</v>
       </c>
       <c r="D469" s="9">
-        <v>5202</v>
+        <v>202</v>
       </c>
       <c r="E469" s="10">
         <v>165000</v>
@@ -24210,7 +24210,7 @@
         <v>203</v>
       </c>
       <c r="D470" s="9">
-        <v>5203</v>
+        <v>203</v>
       </c>
       <c r="E470" s="10">
         <v>165000</v>
@@ -24239,7 +24239,7 @@
         <v>204</v>
       </c>
       <c r="D471" s="9">
-        <v>5204</v>
+        <v>204</v>
       </c>
       <c r="E471" s="10">
         <v>165000</v>
@@ -24268,7 +24268,7 @@
         <v>205</v>
       </c>
       <c r="D472" s="9">
-        <v>5205</v>
+        <v>205</v>
       </c>
       <c r="E472" s="10">
         <v>165000</v>
@@ -24297,7 +24297,7 @@
         <v>302</v>
       </c>
       <c r="D473" s="9">
-        <v>5302</v>
+        <v>302</v>
       </c>
       <c r="E473" s="10">
         <v>165000</v>
@@ -24326,7 +24326,7 @@
         <v>303</v>
       </c>
       <c r="D474" s="9">
-        <v>5303</v>
+        <v>303</v>
       </c>
       <c r="E474" s="10">
         <v>165000</v>
@@ -24355,7 +24355,7 @@
         <v>304</v>
       </c>
       <c r="D475" s="9">
-        <v>5304</v>
+        <v>304</v>
       </c>
       <c r="E475" s="10">
         <v>165000</v>
@@ -24384,7 +24384,7 @@
         <v>305</v>
       </c>
       <c r="D476" s="9">
-        <v>5305</v>
+        <v>305</v>
       </c>
       <c r="E476" s="10">
         <v>165000</v>
@@ -24413,7 +24413,7 @@
         <v>306</v>
       </c>
       <c r="D477" s="9">
-        <v>5306</v>
+        <v>306</v>
       </c>
       <c r="E477" s="10">
         <v>165000</v>
@@ -24442,7 +24442,7 @@
         <v>307</v>
       </c>
       <c r="D478" s="9">
-        <v>5307</v>
+        <v>307</v>
       </c>
       <c r="E478" s="10">
         <v>165000</v>
@@ -24471,7 +24471,7 @@
         <v>401</v>
       </c>
       <c r="D479" s="9">
-        <v>5401</v>
+        <v>401</v>
       </c>
       <c r="E479" s="10">
         <v>165000</v>
@@ -24500,7 +24500,7 @@
         <v>402</v>
       </c>
       <c r="D480" s="9">
-        <v>5402</v>
+        <v>402</v>
       </c>
       <c r="E480" s="10">
         <v>165000</v>
@@ -24529,7 +24529,7 @@
         <v>403</v>
       </c>
       <c r="D481" s="9">
-        <v>5403</v>
+        <v>403</v>
       </c>
       <c r="E481" s="10">
         <v>165000</v>
@@ -24558,7 +24558,7 @@
         <v>404</v>
       </c>
       <c r="D482" s="9">
-        <v>5404</v>
+        <v>404</v>
       </c>
       <c r="E482" s="10">
         <v>165000</v>
@@ -24587,7 +24587,7 @@
         <v>405</v>
       </c>
       <c r="D483" s="9">
-        <v>5405</v>
+        <v>405</v>
       </c>
       <c r="E483" s="10">
         <v>165000</v>
@@ -24616,7 +24616,7 @@
         <v>406</v>
       </c>
       <c r="D484" s="9">
-        <v>5406</v>
+        <v>406</v>
       </c>
       <c r="E484" s="10">
         <v>165000</v>
@@ -24645,7 +24645,7 @@
         <v>407</v>
       </c>
       <c r="D485" s="9">
-        <v>5407</v>
+        <v>407</v>
       </c>
       <c r="E485" s="10">
         <v>165000</v>
@@ -24674,7 +24674,7 @@
         <v>408</v>
       </c>
       <c r="D486" s="9">
-        <v>5408</v>
+        <v>408</v>
       </c>
       <c r="E486" s="10">
         <v>165000</v>
@@ -24703,7 +24703,7 @@
         <v>501</v>
       </c>
       <c r="D487" s="9">
-        <v>5501</v>
+        <v>501</v>
       </c>
       <c r="E487" s="10">
         <v>165000</v>
@@ -24732,7 +24732,7 @@
         <v>502</v>
       </c>
       <c r="D488" s="9">
-        <v>5502</v>
+        <v>502</v>
       </c>
       <c r="E488" s="10">
         <v>165000</v>
@@ -24761,7 +24761,7 @@
         <v>503</v>
       </c>
       <c r="D489" s="9">
-        <v>5503</v>
+        <v>503</v>
       </c>
       <c r="E489" s="10">
         <v>165000</v>
@@ -24790,7 +24790,7 @@
         <v>504</v>
       </c>
       <c r="D490" s="9">
-        <v>5504</v>
+        <v>504</v>
       </c>
       <c r="E490" s="10">
         <v>165000</v>
@@ -24819,7 +24819,7 @@
         <v>505</v>
       </c>
       <c r="D491" s="9">
-        <v>5505</v>
+        <v>505</v>
       </c>
       <c r="E491" s="10">
         <v>165000</v>
@@ -24848,7 +24848,7 @@
         <v>506</v>
       </c>
       <c r="D492" s="9">
-        <v>5506</v>
+        <v>506</v>
       </c>
       <c r="E492" s="10">
         <v>165000</v>
@@ -24877,7 +24877,7 @@
         <v>507</v>
       </c>
       <c r="D493" s="9">
-        <v>5507</v>
+        <v>507</v>
       </c>
       <c r="E493" s="10">
         <v>165000</v>
@@ -24906,7 +24906,7 @@
         <v>508</v>
       </c>
       <c r="D494" s="9">
-        <v>5508</v>
+        <v>508</v>
       </c>
       <c r="E494" s="10">
         <v>165000</v>
@@ -24935,7 +24935,7 @@
         <v>601</v>
       </c>
       <c r="D495" s="9">
-        <v>5601</v>
+        <v>601</v>
       </c>
       <c r="E495" s="10">
         <v>165000</v>
@@ -24964,7 +24964,7 @@
         <v>502</v>
       </c>
       <c r="D496" s="9">
-        <v>5602</v>
+        <v>502</v>
       </c>
       <c r="E496" s="10">
         <v>165000</v>
@@ -24993,7 +24993,7 @@
         <v>603</v>
       </c>
       <c r="D497" s="9">
-        <v>5603</v>
+        <v>603</v>
       </c>
       <c r="E497" s="10">
         <v>165000</v>
@@ -25022,7 +25022,7 @@
         <v>604</v>
       </c>
       <c r="D498" s="9">
-        <v>5604</v>
+        <v>604</v>
       </c>
       <c r="E498" s="10">
         <v>165000</v>
@@ -25051,7 +25051,7 @@
         <v>605</v>
       </c>
       <c r="D499" s="9">
-        <v>5605</v>
+        <v>605</v>
       </c>
       <c r="E499" s="10">
         <v>165000</v>
@@ -25080,7 +25080,7 @@
         <v>606</v>
       </c>
       <c r="D500" s="9">
-        <v>5606</v>
+        <v>606</v>
       </c>
       <c r="E500" s="10">
         <v>165000</v>
@@ -25109,7 +25109,7 @@
         <v>607</v>
       </c>
       <c r="D501" s="9">
-        <v>5607</v>
+        <v>607</v>
       </c>
       <c r="E501" s="10">
         <v>165000</v>
@@ -25138,7 +25138,7 @@
         <v>608</v>
       </c>
       <c r="D502" s="9">
-        <v>5608</v>
+        <v>608</v>
       </c>
       <c r="E502" s="10">
         <v>165000</v>
@@ -25167,7 +25167,7 @@
         <v>701</v>
       </c>
       <c r="D503" s="9">
-        <v>5701</v>
+        <v>701</v>
       </c>
       <c r="E503" s="10">
         <v>165000</v>
@@ -25196,7 +25196,7 @@
         <v>702</v>
       </c>
       <c r="D504" s="9">
-        <v>5702</v>
+        <v>702</v>
       </c>
       <c r="E504" s="10">
         <v>165000</v>
@@ -25225,7 +25225,7 @@
         <v>703</v>
       </c>
       <c r="D505" s="9">
-        <v>5703</v>
+        <v>703</v>
       </c>
       <c r="E505" s="10">
         <v>165000</v>
@@ -25254,7 +25254,7 @@
         <v>704</v>
       </c>
       <c r="D506" s="9">
-        <v>5704</v>
+        <v>704</v>
       </c>
       <c r="E506" s="10">
         <v>165000</v>
@@ -25283,7 +25283,7 @@
         <v>705</v>
       </c>
       <c r="D507" s="9">
-        <v>5705</v>
+        <v>705</v>
       </c>
       <c r="E507" s="10">
         <v>165000</v>
@@ -25312,7 +25312,7 @@
         <v>706</v>
       </c>
       <c r="D508" s="9">
-        <v>5706</v>
+        <v>706</v>
       </c>
       <c r="E508" s="10">
         <v>165000</v>
@@ -25341,7 +25341,7 @@
         <v>707</v>
       </c>
       <c r="D509" s="9">
-        <v>5707</v>
+        <v>707</v>
       </c>
       <c r="E509" s="10">
         <v>165000</v>
@@ -25370,7 +25370,7 @@
         <v>708</v>
       </c>
       <c r="D510" s="9">
-        <v>5708</v>
+        <v>708</v>
       </c>
       <c r="E510" s="10">
         <v>165000</v>
@@ -25399,7 +25399,7 @@
         <v>801</v>
       </c>
       <c r="D511" s="9">
-        <v>5801</v>
+        <v>801</v>
       </c>
       <c r="E511" s="10">
         <v>165000</v>
@@ -25428,7 +25428,7 @@
         <v>802</v>
       </c>
       <c r="D512" s="9">
-        <v>5802</v>
+        <v>802</v>
       </c>
       <c r="E512" s="10">
         <v>165000</v>
@@ -25457,7 +25457,7 @@
         <v>803</v>
       </c>
       <c r="D513" s="9">
-        <v>5803</v>
+        <v>803</v>
       </c>
       <c r="E513" s="10">
         <v>165000</v>
@@ -25486,7 +25486,7 @@
         <v>804</v>
       </c>
       <c r="D514" s="9">
-        <v>5804</v>
+        <v>804</v>
       </c>
       <c r="E514" s="10">
         <v>165000</v>
@@ -25515,7 +25515,7 @@
         <v>805</v>
       </c>
       <c r="D515" s="9">
-        <v>5805</v>
+        <v>805</v>
       </c>
       <c r="E515" s="10">
         <v>165000</v>
@@ -25544,7 +25544,7 @@
         <v>806</v>
       </c>
       <c r="D516" s="9">
-        <v>5806</v>
+        <v>806</v>
       </c>
       <c r="E516" s="10">
         <v>165000</v>
@@ -25573,7 +25573,7 @@
         <v>807</v>
       </c>
       <c r="D517" s="9">
-        <v>5807</v>
+        <v>807</v>
       </c>
       <c r="E517" s="10">
         <v>165000</v>
@@ -25602,7 +25602,7 @@
         <v>808</v>
       </c>
       <c r="D518" s="9">
-        <v>5808</v>
+        <v>808</v>
       </c>
       <c r="E518" s="10">
         <v>165000</v>
@@ -25631,7 +25631,7 @@
         <v>901</v>
       </c>
       <c r="D519" s="9">
-        <v>5901</v>
+        <v>901</v>
       </c>
       <c r="E519" s="10">
         <v>165000</v>
@@ -25660,7 +25660,7 @@
         <v>902</v>
       </c>
       <c r="D520" s="9">
-        <v>5902</v>
+        <v>902</v>
       </c>
       <c r="E520" s="10">
         <v>165000</v>
@@ -25689,7 +25689,7 @@
         <v>903</v>
       </c>
       <c r="D521" s="9">
-        <v>5903</v>
+        <v>903</v>
       </c>
       <c r="E521" s="10">
         <v>165000</v>
@@ -25718,7 +25718,7 @@
         <v>904</v>
       </c>
       <c r="D522" s="9">
-        <v>5904</v>
+        <v>904</v>
       </c>
       <c r="E522" s="10">
         <v>165000</v>
@@ -25747,7 +25747,7 @@
         <v>905</v>
       </c>
       <c r="D523" s="9">
-        <v>5905</v>
+        <v>905</v>
       </c>
       <c r="E523" s="10">
         <v>165000</v>
@@ -25776,7 +25776,7 @@
         <v>906</v>
       </c>
       <c r="D524" s="9">
-        <v>5906</v>
+        <v>906</v>
       </c>
       <c r="E524" s="10">
         <v>165000</v>
@@ -25805,7 +25805,7 @@
         <v>907</v>
       </c>
       <c r="D525" s="9">
-        <v>5907</v>
+        <v>907</v>
       </c>
       <c r="E525" s="10">
         <v>165000</v>
@@ -25834,7 +25834,7 @@
         <v>908</v>
       </c>
       <c r="D526" s="9">
-        <v>5908</v>
+        <v>908</v>
       </c>
       <c r="E526" s="10">
         <v>165000</v>
@@ -25863,7 +25863,7 @@
         <v>1001</v>
       </c>
       <c r="D527" s="9">
-        <v>51001</v>
+        <v>1001</v>
       </c>
       <c r="E527" s="10">
         <v>165000</v>
@@ -25892,7 +25892,7 @@
         <v>1002</v>
       </c>
       <c r="D528" s="9">
-        <v>51002</v>
+        <v>1002</v>
       </c>
       <c r="E528" s="10">
         <v>165000</v>
@@ -25921,7 +25921,7 @@
         <v>1003</v>
       </c>
       <c r="D529" s="9">
-        <v>51003</v>
+        <v>1003</v>
       </c>
       <c r="E529" s="10">
         <v>165000</v>
@@ -25950,7 +25950,7 @@
         <v>1004</v>
       </c>
       <c r="D530" s="9">
-        <v>51004</v>
+        <v>1004</v>
       </c>
       <c r="E530" s="10">
         <v>165000</v>
@@ -25979,7 +25979,7 @@
         <v>1005</v>
       </c>
       <c r="D531" s="9">
-        <v>51005</v>
+        <v>1005</v>
       </c>
       <c r="E531" s="10">
         <v>165000</v>
@@ -26008,7 +26008,7 @@
         <v>1006</v>
       </c>
       <c r="D532" s="9">
-        <v>51006</v>
+        <v>1006</v>
       </c>
       <c r="E532" s="10">
         <v>165000</v>
@@ -26037,7 +26037,7 @@
         <v>1007</v>
       </c>
       <c r="D533" s="9">
-        <v>51007</v>
+        <v>1007</v>
       </c>
       <c r="E533" s="10">
         <v>165000</v>
@@ -26066,7 +26066,7 @@
         <v>1008</v>
       </c>
       <c r="D534" s="9">
-        <v>51008</v>
+        <v>1008</v>
       </c>
       <c r="E534" s="10">
         <v>165000</v>
@@ -26095,7 +26095,7 @@
         <v>1101</v>
       </c>
       <c r="D535" s="9">
-        <v>51101</v>
+        <v>1101</v>
       </c>
       <c r="E535" s="10">
         <v>165000</v>
@@ -26124,7 +26124,7 @@
         <v>1102</v>
       </c>
       <c r="D536" s="9">
-        <v>51102</v>
+        <v>1102</v>
       </c>
       <c r="E536" s="10">
         <v>165000</v>
@@ -26153,7 +26153,7 @@
         <v>1103</v>
       </c>
       <c r="D537" s="9">
-        <v>51103</v>
+        <v>1103</v>
       </c>
       <c r="E537" s="10">
         <v>165000</v>
@@ -26182,7 +26182,7 @@
         <v>1104</v>
       </c>
       <c r="D538" s="9">
-        <v>51104</v>
+        <v>1104</v>
       </c>
       <c r="E538" s="10">
         <v>165000</v>
@@ -26211,7 +26211,7 @@
         <v>1105</v>
       </c>
       <c r="D539" s="9">
-        <v>51105</v>
+        <v>1105</v>
       </c>
       <c r="E539" s="10">
         <v>165000</v>
@@ -26240,7 +26240,7 @@
         <v>1106</v>
       </c>
       <c r="D540" s="9">
-        <v>51106</v>
+        <v>1106</v>
       </c>
       <c r="E540" s="10">
         <v>165000</v>
@@ -26269,7 +26269,7 @@
         <v>1107</v>
       </c>
       <c r="D541" s="9">
-        <v>51107</v>
+        <v>1107</v>
       </c>
       <c r="E541" s="10">
         <v>165000</v>
@@ -26298,7 +26298,7 @@
         <v>1108</v>
       </c>
       <c r="D542" s="9">
-        <v>51108</v>
+        <v>1108</v>
       </c>
       <c r="E542" s="10">
         <v>165000</v>
@@ -26327,7 +26327,7 @@
         <v>1201</v>
       </c>
       <c r="D543" s="9">
-        <v>51201</v>
+        <v>1201</v>
       </c>
       <c r="E543" s="10">
         <v>165000</v>
@@ -26356,7 +26356,7 @@
         <v>1202</v>
       </c>
       <c r="D544" s="9">
-        <v>51202</v>
+        <v>1202</v>
       </c>
       <c r="E544" s="10">
         <v>165000</v>
@@ -26385,7 +26385,7 @@
         <v>1203</v>
       </c>
       <c r="D545" s="9">
-        <v>51203</v>
+        <v>1203</v>
       </c>
       <c r="E545" s="10">
         <v>165000</v>
@@ -26414,7 +26414,7 @@
         <v>1204</v>
       </c>
       <c r="D546" s="9">
-        <v>51204</v>
+        <v>1204</v>
       </c>
       <c r="E546" s="10">
         <v>165000</v>
@@ -26443,7 +26443,7 @@
         <v>1205</v>
       </c>
       <c r="D547" s="9">
-        <v>51205</v>
+        <v>1205</v>
       </c>
       <c r="E547" s="10">
         <v>165000</v>
@@ -26472,7 +26472,7 @@
         <v>1206</v>
       </c>
       <c r="D548" s="9">
-        <v>51206</v>
+        <v>1206</v>
       </c>
       <c r="E548" s="10">
         <v>165000</v>
@@ -26501,7 +26501,7 @@
         <v>1207</v>
       </c>
       <c r="D549" s="9">
-        <v>51207</v>
+        <v>1207</v>
       </c>
       <c r="E549" s="10">
         <v>165000</v>
@@ -26530,7 +26530,7 @@
         <v>1208</v>
       </c>
       <c r="D550" s="9">
-        <v>51208</v>
+        <v>1208</v>
       </c>
       <c r="E550" s="10">
         <v>165000</v>
@@ -26559,7 +26559,7 @@
         <v>1301</v>
       </c>
       <c r="D551" s="9">
-        <v>51301</v>
+        <v>1301</v>
       </c>
       <c r="E551" s="10">
         <v>165000</v>
@@ -26588,7 +26588,7 @@
         <v>1302</v>
       </c>
       <c r="D552" s="9">
-        <v>51302</v>
+        <v>1302</v>
       </c>
       <c r="E552" s="10">
         <v>165000</v>
@@ -26617,7 +26617,7 @@
         <v>1303</v>
       </c>
       <c r="D553" s="9">
-        <v>51303</v>
+        <v>1303</v>
       </c>
       <c r="E553" s="10">
         <v>165000</v>
@@ -26646,7 +26646,7 @@
         <v>1304</v>
       </c>
       <c r="D554" s="9">
-        <v>51304</v>
+        <v>1304</v>
       </c>
       <c r="E554" s="10">
         <v>165000</v>
@@ -26675,7 +26675,7 @@
         <v>1305</v>
       </c>
       <c r="D555" s="9">
-        <v>51305</v>
+        <v>1305</v>
       </c>
       <c r="E555" s="10">
         <v>165000</v>
@@ -26704,7 +26704,7 @@
         <v>1306</v>
       </c>
       <c r="D556" s="9">
-        <v>51306</v>
+        <v>1306</v>
       </c>
       <c r="E556" s="10">
         <v>165000</v>
@@ -26733,7 +26733,7 @@
         <v>1307</v>
       </c>
       <c r="D557" s="9">
-        <v>51307</v>
+        <v>1307</v>
       </c>
       <c r="E557" s="10">
         <v>165000</v>
@@ -26762,7 +26762,7 @@
         <v>1308</v>
       </c>
       <c r="D558" s="9">
-        <v>51308</v>
+        <v>1308</v>
       </c>
       <c r="E558" s="10">
         <v>165000</v>
@@ -26791,7 +26791,7 @@
         <v>1401</v>
       </c>
       <c r="D559" s="9">
-        <v>51401</v>
+        <v>1401</v>
       </c>
       <c r="E559" s="10">
         <v>165000</v>
@@ -26820,7 +26820,7 @@
         <v>1402</v>
       </c>
       <c r="D560" s="9">
-        <v>51402</v>
+        <v>1402</v>
       </c>
       <c r="E560" s="10">
         <v>165000</v>
@@ -26849,7 +26849,7 @@
         <v>1403</v>
       </c>
       <c r="D561" s="9">
-        <v>51403</v>
+        <v>1403</v>
       </c>
       <c r="E561" s="10">
         <v>165000</v>
@@ -26878,7 +26878,7 @@
         <v>1404</v>
       </c>
       <c r="D562" s="9">
-        <v>51404</v>
+        <v>1404</v>
       </c>
       <c r="E562" s="10">
         <v>165000</v>
@@ -26907,7 +26907,7 @@
         <v>1405</v>
       </c>
       <c r="D563" s="9">
-        <v>51405</v>
+        <v>1405</v>
       </c>
       <c r="E563" s="10">
         <v>165000</v>
@@ -26936,7 +26936,7 @@
         <v>1406</v>
       </c>
       <c r="D564" s="9">
-        <v>51406</v>
+        <v>1406</v>
       </c>
       <c r="E564" s="10">
         <v>165000</v>
@@ -26965,7 +26965,7 @@
         <v>1407</v>
       </c>
       <c r="D565" s="9">
-        <v>51407</v>
+        <v>1407</v>
       </c>
       <c r="E565" s="10">
         <v>165000</v>
@@ -26994,7 +26994,7 @@
         <v>1408</v>
       </c>
       <c r="D566" s="9">
-        <v>51408</v>
+        <v>1408</v>
       </c>
       <c r="E566" s="10">
         <v>165000</v>
@@ -27023,7 +27023,7 @@
         <v>1501</v>
       </c>
       <c r="D567" s="9">
-        <v>51501</v>
+        <v>1501</v>
       </c>
       <c r="E567" s="10">
         <v>165000</v>
@@ -27052,7 +27052,7 @@
         <v>1502</v>
       </c>
       <c r="D568" s="9">
-        <v>51502</v>
+        <v>1502</v>
       </c>
       <c r="E568" s="10">
         <v>165000</v>
@@ -27081,7 +27081,7 @@
         <v>1503</v>
       </c>
       <c r="D569" s="9">
-        <v>51503</v>
+        <v>1503</v>
       </c>
       <c r="E569" s="10">
         <v>165000</v>
@@ -27110,7 +27110,7 @@
         <v>1504</v>
       </c>
       <c r="D570" s="9">
-        <v>51504</v>
+        <v>1504</v>
       </c>
       <c r="E570" s="10">
         <v>165000</v>
@@ -27139,7 +27139,7 @@
         <v>1505</v>
       </c>
       <c r="D571" s="9">
-        <v>51505</v>
+        <v>1505</v>
       </c>
       <c r="E571" s="10">
         <v>165000</v>
@@ -27168,7 +27168,7 @@
         <v>1506</v>
       </c>
       <c r="D572" s="9">
-        <v>51506</v>
+        <v>1506</v>
       </c>
       <c r="E572" s="10">
         <v>165000</v>
@@ -27197,7 +27197,7 @@
         <v>1507</v>
       </c>
       <c r="D573" s="9">
-        <v>51507</v>
+        <v>1507</v>
       </c>
       <c r="E573" s="10">
         <v>165000</v>
@@ -27226,7 +27226,7 @@
         <v>1508</v>
       </c>
       <c r="D574" s="9">
-        <v>51508</v>
+        <v>1508</v>
       </c>
       <c r="E574" s="10">
         <v>165000</v>
@@ -27255,7 +27255,7 @@
         <v>102</v>
       </c>
       <c r="D575" s="9">
-        <v>6102</v>
+        <v>102</v>
       </c>
       <c r="E575" s="10">
         <v>164000</v>
@@ -27284,7 +27284,7 @@
         <v>103</v>
       </c>
       <c r="D576" s="9">
-        <v>6103</v>
+        <v>103</v>
       </c>
       <c r="E576" s="10">
         <v>153000</v>
@@ -27313,7 +27313,7 @@
         <v>104</v>
       </c>
       <c r="D577" s="9">
-        <v>6104</v>
+        <v>104</v>
       </c>
       <c r="E577" s="10">
         <v>164000</v>
@@ -27342,7 +27342,7 @@
         <v>105</v>
       </c>
       <c r="D578" s="9">
-        <v>6105</v>
+        <v>105</v>
       </c>
       <c r="E578" s="10">
         <v>164000</v>
@@ -27371,7 +27371,7 @@
         <v>202</v>
       </c>
       <c r="D579" s="9">
-        <v>6202</v>
+        <v>202</v>
       </c>
       <c r="E579" s="10">
         <v>164000</v>
@@ -27400,7 +27400,7 @@
         <v>203</v>
       </c>
       <c r="D580" s="9">
-        <v>6203</v>
+        <v>203</v>
       </c>
       <c r="E580" s="10">
         <v>164000</v>
@@ -27429,7 +27429,7 @@
         <v>204</v>
       </c>
       <c r="D581" s="9">
-        <v>6204</v>
+        <v>204</v>
       </c>
       <c r="E581" s="10">
         <v>164000</v>
@@ -27458,7 +27458,7 @@
         <v>205</v>
       </c>
       <c r="D582" s="9">
-        <v>6205</v>
+        <v>205</v>
       </c>
       <c r="E582" s="10">
         <v>164000</v>
@@ -27487,7 +27487,7 @@
         <v>206</v>
       </c>
       <c r="D583" s="9">
-        <v>6206</v>
+        <v>206</v>
       </c>
       <c r="E583" s="10">
         <v>164000</v>
@@ -27516,7 +27516,7 @@
         <v>207</v>
       </c>
       <c r="D584" s="9">
-        <v>6207</v>
+        <v>207</v>
       </c>
       <c r="E584" s="10">
         <v>164000</v>
@@ -27545,7 +27545,7 @@
         <v>301</v>
       </c>
       <c r="D585" s="9">
-        <v>6301</v>
+        <v>301</v>
       </c>
       <c r="E585" s="10">
         <v>164000</v>
@@ -27574,7 +27574,7 @@
         <v>302</v>
       </c>
       <c r="D586" s="9">
-        <v>6302</v>
+        <v>302</v>
       </c>
       <c r="E586" s="10">
         <v>164000</v>
@@ -27603,7 +27603,7 @@
         <v>303</v>
       </c>
       <c r="D587" s="9">
-        <v>6303</v>
+        <v>303</v>
       </c>
       <c r="E587" s="10">
         <v>164000</v>
@@ -27632,7 +27632,7 @@
         <v>304</v>
       </c>
       <c r="D588" s="9">
-        <v>6304</v>
+        <v>304</v>
       </c>
       <c r="E588" s="10">
         <v>164000</v>
@@ -27661,7 +27661,7 @@
         <v>305</v>
       </c>
       <c r="D589" s="9">
-        <v>6305</v>
+        <v>305</v>
       </c>
       <c r="E589" s="10">
         <v>164000</v>
@@ -27690,7 +27690,7 @@
         <v>306</v>
       </c>
       <c r="D590" s="9">
-        <v>6306</v>
+        <v>306</v>
       </c>
       <c r="E590" s="10">
         <v>164000</v>
@@ -27719,7 +27719,7 @@
         <v>307</v>
       </c>
       <c r="D591" s="9">
-        <v>6307</v>
+        <v>307</v>
       </c>
       <c r="E591" s="10">
         <v>164000</v>
@@ -27748,7 +27748,7 @@
         <v>308</v>
       </c>
       <c r="D592" s="9">
-        <v>6308</v>
+        <v>308</v>
       </c>
       <c r="E592" s="10">
         <v>164000</v>
@@ -27777,7 +27777,7 @@
         <v>401</v>
       </c>
       <c r="D593" s="9">
-        <v>6401</v>
+        <v>401</v>
       </c>
       <c r="E593" s="10">
         <v>164000</v>
@@ -27806,7 +27806,7 @@
         <v>402</v>
       </c>
       <c r="D594" s="9">
-        <v>6402</v>
+        <v>402</v>
       </c>
       <c r="E594" s="10">
         <v>164000</v>
@@ -27835,7 +27835,7 @@
         <v>403</v>
       </c>
       <c r="D595" s="9">
-        <v>6403</v>
+        <v>403</v>
       </c>
       <c r="E595" s="10">
         <v>164000</v>
@@ -27864,7 +27864,7 @@
         <v>404</v>
       </c>
       <c r="D596" s="9">
-        <v>6404</v>
+        <v>404</v>
       </c>
       <c r="E596" s="10">
         <v>164000</v>
@@ -27893,7 +27893,7 @@
         <v>405</v>
       </c>
       <c r="D597" s="9">
-        <v>6405</v>
+        <v>405</v>
       </c>
       <c r="E597" s="10">
         <v>164000</v>
@@ -27922,7 +27922,7 @@
         <v>406</v>
       </c>
       <c r="D598" s="9">
-        <v>6406</v>
+        <v>406</v>
       </c>
       <c r="E598" s="10">
         <v>164000</v>
@@ -27951,7 +27951,7 @@
         <v>407</v>
       </c>
       <c r="D599" s="9">
-        <v>6407</v>
+        <v>407</v>
       </c>
       <c r="E599" s="10">
         <v>164000</v>
@@ -27980,7 +27980,7 @@
         <v>408</v>
       </c>
       <c r="D600" s="9">
-        <v>6408</v>
+        <v>408</v>
       </c>
       <c r="E600" s="10">
         <v>164000</v>
@@ -28009,7 +28009,7 @@
         <v>501</v>
       </c>
       <c r="D601" s="9">
-        <v>6501</v>
+        <v>501</v>
       </c>
       <c r="E601" s="10">
         <v>164000</v>
@@ -28038,7 +28038,7 @@
         <v>502</v>
       </c>
       <c r="D602" s="9">
-        <v>6502</v>
+        <v>502</v>
       </c>
       <c r="E602" s="10">
         <v>164000</v>
@@ -28067,7 +28067,7 @@
         <v>503</v>
       </c>
       <c r="D603" s="9">
-        <v>6503</v>
+        <v>503</v>
       </c>
       <c r="E603" s="10">
         <v>164000</v>
@@ -28096,7 +28096,7 @@
         <v>504</v>
       </c>
       <c r="D604" s="9">
-        <v>6504</v>
+        <v>504</v>
       </c>
       <c r="E604" s="10">
         <v>164000</v>
@@ -28125,7 +28125,7 @@
         <v>505</v>
       </c>
       <c r="D605" s="9">
-        <v>6505</v>
+        <v>505</v>
       </c>
       <c r="E605" s="10">
         <v>164000</v>
@@ -28154,7 +28154,7 @@
         <v>506</v>
       </c>
       <c r="D606" s="9">
-        <v>6506</v>
+        <v>506</v>
       </c>
       <c r="E606" s="10">
         <v>164000</v>
@@ -28183,7 +28183,7 @@
         <v>507</v>
       </c>
       <c r="D607" s="9">
-        <v>6507</v>
+        <v>507</v>
       </c>
       <c r="E607" s="10">
         <v>164000</v>
@@ -28212,7 +28212,7 @@
         <v>508</v>
       </c>
       <c r="D608" s="9">
-        <v>6508</v>
+        <v>508</v>
       </c>
       <c r="E608" s="10">
         <v>164000</v>
@@ -28241,7 +28241,7 @@
         <v>601</v>
       </c>
       <c r="D609" s="9">
-        <v>6601</v>
+        <v>601</v>
       </c>
       <c r="E609" s="10">
         <v>164000</v>
@@ -28270,7 +28270,7 @@
         <v>502</v>
       </c>
       <c r="D610" s="9">
-        <v>6602</v>
+        <v>502</v>
       </c>
       <c r="E610" s="10">
         <v>164000</v>
@@ -28299,7 +28299,7 @@
         <v>603</v>
       </c>
       <c r="D611" s="9">
-        <v>6603</v>
+        <v>603</v>
       </c>
       <c r="E611" s="10">
         <v>164000</v>
@@ -28328,7 +28328,7 @@
         <v>604</v>
       </c>
       <c r="D612" s="9">
-        <v>6604</v>
+        <v>604</v>
       </c>
       <c r="E612" s="10">
         <v>164000</v>
@@ -28357,7 +28357,7 @@
         <v>605</v>
       </c>
       <c r="D613" s="9">
-        <v>6605</v>
+        <v>605</v>
       </c>
       <c r="E613" s="10">
         <v>164000</v>
@@ -28386,7 +28386,7 @@
         <v>606</v>
       </c>
       <c r="D614" s="9">
-        <v>6606</v>
+        <v>606</v>
       </c>
       <c r="E614" s="10">
         <v>164000</v>
@@ -28415,7 +28415,7 @@
         <v>607</v>
       </c>
       <c r="D615" s="9">
-        <v>6607</v>
+        <v>607</v>
       </c>
       <c r="E615" s="10">
         <v>164000</v>
@@ -28444,7 +28444,7 @@
         <v>608</v>
       </c>
       <c r="D616" s="9">
-        <v>6608</v>
+        <v>608</v>
       </c>
       <c r="E616" s="10">
         <v>164000</v>
@@ -28473,7 +28473,7 @@
         <v>701</v>
       </c>
       <c r="D617" s="9">
-        <v>6701</v>
+        <v>701</v>
       </c>
       <c r="E617" s="10">
         <v>164000</v>
@@ -28502,7 +28502,7 @@
         <v>702</v>
       </c>
       <c r="D618" s="9">
-        <v>6702</v>
+        <v>702</v>
       </c>
       <c r="E618" s="10">
         <v>164000</v>
@@ -28531,7 +28531,7 @@
         <v>703</v>
       </c>
       <c r="D619" s="9">
-        <v>6703</v>
+        <v>703</v>
       </c>
       <c r="E619" s="10">
         <v>164000</v>
@@ -28560,7 +28560,7 @@
         <v>704</v>
       </c>
       <c r="D620" s="9">
-        <v>6704</v>
+        <v>704</v>
       </c>
       <c r="E620" s="10">
         <v>164000</v>
@@ -28589,7 +28589,7 @@
         <v>705</v>
       </c>
       <c r="D621" s="9">
-        <v>6705</v>
+        <v>705</v>
       </c>
       <c r="E621" s="10">
         <v>164000</v>
@@ -28618,7 +28618,7 @@
         <v>706</v>
       </c>
       <c r="D622" s="9">
-        <v>6706</v>
+        <v>706</v>
       </c>
       <c r="E622" s="10">
         <v>164000</v>
@@ -28647,7 +28647,7 @@
         <v>707</v>
       </c>
       <c r="D623" s="9">
-        <v>6707</v>
+        <v>707</v>
       </c>
       <c r="E623" s="10">
         <v>164000</v>
@@ -28676,7 +28676,7 @@
         <v>708</v>
       </c>
       <c r="D624" s="9">
-        <v>6708</v>
+        <v>708</v>
       </c>
       <c r="E624" s="10">
         <v>164000</v>
@@ -28705,7 +28705,7 @@
         <v>801</v>
       </c>
       <c r="D625" s="9">
-        <v>6801</v>
+        <v>801</v>
       </c>
       <c r="E625" s="10">
         <v>164000</v>
@@ -28734,7 +28734,7 @@
         <v>802</v>
       </c>
       <c r="D626" s="9">
-        <v>6802</v>
+        <v>802</v>
       </c>
       <c r="E626" s="10">
         <v>164000</v>
@@ -28763,7 +28763,7 @@
         <v>803</v>
       </c>
       <c r="D627" s="9">
-        <v>6803</v>
+        <v>803</v>
       </c>
       <c r="E627" s="10">
         <v>164000</v>
@@ -28792,7 +28792,7 @@
         <v>804</v>
       </c>
       <c r="D628" s="9">
-        <v>6804</v>
+        <v>804</v>
       </c>
       <c r="E628" s="10">
         <v>164000</v>
@@ -28821,7 +28821,7 @@
         <v>805</v>
       </c>
       <c r="D629" s="9">
-        <v>6805</v>
+        <v>805</v>
       </c>
       <c r="E629" s="10">
         <v>164000</v>
@@ -28850,7 +28850,7 @@
         <v>806</v>
       </c>
       <c r="D630" s="9">
-        <v>6806</v>
+        <v>806</v>
       </c>
       <c r="E630" s="10">
         <v>164000</v>
@@ -28879,7 +28879,7 @@
         <v>807</v>
       </c>
       <c r="D631" s="9">
-        <v>6807</v>
+        <v>807</v>
       </c>
       <c r="E631" s="10">
         <v>164000</v>
@@ -28908,7 +28908,7 @@
         <v>808</v>
       </c>
       <c r="D632" s="9">
-        <v>6808</v>
+        <v>808</v>
       </c>
       <c r="E632" s="10">
         <v>164000</v>
@@ -28937,7 +28937,7 @@
         <v>901</v>
       </c>
       <c r="D633" s="9">
-        <v>6901</v>
+        <v>901</v>
       </c>
       <c r="E633" s="10">
         <v>164000</v>
@@ -28966,7 +28966,7 @@
         <v>902</v>
       </c>
       <c r="D634" s="9">
-        <v>6902</v>
+        <v>902</v>
       </c>
       <c r="E634" s="10">
         <v>164000</v>
@@ -28995,7 +28995,7 @@
         <v>903</v>
       </c>
       <c r="D635" s="9">
-        <v>6903</v>
+        <v>903</v>
       </c>
       <c r="E635" s="10">
         <v>164000</v>
@@ -29024,7 +29024,7 @@
         <v>904</v>
       </c>
       <c r="D636" s="9">
-        <v>6904</v>
+        <v>904</v>
       </c>
       <c r="E636" s="10">
         <v>164000</v>
@@ -29053,7 +29053,7 @@
         <v>905</v>
       </c>
       <c r="D637" s="9">
-        <v>6905</v>
+        <v>905</v>
       </c>
       <c r="E637" s="10">
         <v>164000</v>
@@ -29082,7 +29082,7 @@
         <v>906</v>
       </c>
       <c r="D638" s="9">
-        <v>6906</v>
+        <v>906</v>
       </c>
       <c r="E638" s="10">
         <v>164000</v>
@@ -29111,7 +29111,7 @@
         <v>907</v>
       </c>
       <c r="D639" s="9">
-        <v>6907</v>
+        <v>907</v>
       </c>
       <c r="E639" s="10">
         <v>164000</v>
@@ -29140,7 +29140,7 @@
         <v>908</v>
       </c>
       <c r="D640" s="9">
-        <v>6908</v>
+        <v>908</v>
       </c>
       <c r="E640" s="10">
         <v>164000</v>
@@ -29169,7 +29169,7 @@
         <v>1001</v>
       </c>
       <c r="D641" s="9">
-        <v>61001</v>
+        <v>1001</v>
       </c>
       <c r="E641" s="10">
         <v>164000</v>
@@ -29198,7 +29198,7 @@
         <v>1002</v>
       </c>
       <c r="D642" s="9">
-        <v>61002</v>
+        <v>1002</v>
       </c>
       <c r="E642" s="10">
         <v>164000</v>
@@ -29227,7 +29227,7 @@
         <v>1003</v>
       </c>
       <c r="D643" s="9">
-        <v>61003</v>
+        <v>1003</v>
       </c>
       <c r="E643" s="10">
         <v>164000</v>
@@ -29256,7 +29256,7 @@
         <v>1004</v>
       </c>
       <c r="D644" s="9">
-        <v>61004</v>
+        <v>1004</v>
       </c>
       <c r="E644" s="10">
         <v>164000</v>
@@ -29285,7 +29285,7 @@
         <v>1005</v>
       </c>
       <c r="D645" s="9">
-        <v>61005</v>
+        <v>1005</v>
       </c>
       <c r="E645" s="10">
         <v>164000</v>
@@ -29314,7 +29314,7 @@
         <v>1006</v>
       </c>
       <c r="D646" s="9">
-        <v>61006</v>
+        <v>1006</v>
       </c>
       <c r="E646" s="10">
         <v>164000</v>
@@ -29343,7 +29343,7 @@
         <v>1007</v>
       </c>
       <c r="D647" s="9">
-        <v>61007</v>
+        <v>1007</v>
       </c>
       <c r="E647" s="10">
         <v>164000</v>
@@ -29372,7 +29372,7 @@
         <v>1008</v>
       </c>
       <c r="D648" s="9">
-        <v>61008</v>
+        <v>1008</v>
       </c>
       <c r="E648" s="10">
         <v>164000</v>
@@ -29401,7 +29401,7 @@
         <v>1101</v>
       </c>
       <c r="D649" s="9">
-        <v>61101</v>
+        <v>1101</v>
       </c>
       <c r="E649" s="10">
         <v>164000</v>
@@ -29430,7 +29430,7 @@
         <v>1102</v>
       </c>
       <c r="D650" s="9">
-        <v>61102</v>
+        <v>1102</v>
       </c>
       <c r="E650" s="10">
         <v>164000</v>
@@ -29459,7 +29459,7 @@
         <v>1103</v>
       </c>
       <c r="D651" s="9">
-        <v>61103</v>
+        <v>1103</v>
       </c>
       <c r="E651" s="10">
         <v>164000</v>
@@ -29488,7 +29488,7 @@
         <v>1104</v>
       </c>
       <c r="D652" s="9">
-        <v>61104</v>
+        <v>1104</v>
       </c>
       <c r="E652" s="10">
         <v>164000</v>
@@ -29517,7 +29517,7 @@
         <v>1105</v>
       </c>
       <c r="D653" s="9">
-        <v>61105</v>
+        <v>1105</v>
       </c>
       <c r="E653" s="10">
         <v>164000</v>
@@ -29546,7 +29546,7 @@
         <v>1106</v>
       </c>
       <c r="D654" s="9">
-        <v>61106</v>
+        <v>1106</v>
       </c>
       <c r="E654" s="10">
         <v>164000</v>
@@ -29575,7 +29575,7 @@
         <v>1107</v>
       </c>
       <c r="D655" s="9">
-        <v>61107</v>
+        <v>1107</v>
       </c>
       <c r="E655" s="10">
         <v>164000</v>
@@ -29604,7 +29604,7 @@
         <v>1108</v>
       </c>
       <c r="D656" s="9">
-        <v>61108</v>
+        <v>1108</v>
       </c>
       <c r="E656" s="10">
         <v>164000</v>
@@ -29633,7 +29633,7 @@
         <v>1201</v>
       </c>
       <c r="D657" s="9">
-        <v>61201</v>
+        <v>1201</v>
       </c>
       <c r="E657" s="10">
         <v>164000</v>
@@ -29662,7 +29662,7 @@
         <v>1202</v>
       </c>
       <c r="D658" s="9">
-        <v>61202</v>
+        <v>1202</v>
       </c>
       <c r="E658" s="10">
         <v>164000</v>
@@ -29691,7 +29691,7 @@
         <v>1203</v>
       </c>
       <c r="D659" s="9">
-        <v>61203</v>
+        <v>1203</v>
       </c>
       <c r="E659" s="10">
         <v>164000</v>
@@ -29720,7 +29720,7 @@
         <v>1204</v>
       </c>
       <c r="D660" s="9">
-        <v>61204</v>
+        <v>1204</v>
       </c>
       <c r="E660" s="10">
         <v>164000</v>
@@ -29749,7 +29749,7 @@
         <v>1205</v>
       </c>
       <c r="D661" s="9">
-        <v>61205</v>
+        <v>1205</v>
       </c>
       <c r="E661" s="10">
         <v>164000</v>
@@ -29778,7 +29778,7 @@
         <v>1206</v>
       </c>
       <c r="D662" s="9">
-        <v>61206</v>
+        <v>1206</v>
       </c>
       <c r="E662" s="10">
         <v>164000</v>
@@ -29807,7 +29807,7 @@
         <v>1207</v>
       </c>
       <c r="D663" s="9">
-        <v>61207</v>
+        <v>1207</v>
       </c>
       <c r="E663" s="10">
         <v>164000</v>
@@ -29836,7 +29836,7 @@
         <v>1208</v>
       </c>
       <c r="D664" s="9">
-        <v>61208</v>
+        <v>1208</v>
       </c>
       <c r="E664" s="10">
         <v>164000</v>
@@ -29865,7 +29865,7 @@
         <v>1301</v>
       </c>
       <c r="D665" s="9">
-        <v>61301</v>
+        <v>1301</v>
       </c>
       <c r="E665" s="10">
         <v>164000</v>
@@ -29894,7 +29894,7 @@
         <v>1302</v>
       </c>
       <c r="D666" s="9">
-        <v>61302</v>
+        <v>1302</v>
       </c>
       <c r="E666" s="10">
         <v>164000</v>
@@ -29923,7 +29923,7 @@
         <v>1303</v>
       </c>
       <c r="D667" s="9">
-        <v>61303</v>
+        <v>1303</v>
       </c>
       <c r="E667" s="10">
         <v>164000</v>
@@ -29952,7 +29952,7 @@
         <v>1304</v>
       </c>
       <c r="D668" s="9">
-        <v>61304</v>
+        <v>1304</v>
       </c>
       <c r="E668" s="10">
         <v>164000</v>
@@ -29981,7 +29981,7 @@
         <v>1305</v>
       </c>
       <c r="D669" s="9">
-        <v>61305</v>
+        <v>1305</v>
       </c>
       <c r="E669" s="10">
         <v>164000</v>
@@ -30010,7 +30010,7 @@
         <v>1306</v>
       </c>
       <c r="D670" s="9">
-        <v>61306</v>
+        <v>1306</v>
       </c>
       <c r="E670" s="10">
         <v>164000</v>
@@ -30039,7 +30039,7 @@
         <v>1307</v>
       </c>
       <c r="D671" s="9">
-        <v>61307</v>
+        <v>1307</v>
       </c>
       <c r="E671" s="10">
         <v>164000</v>
@@ -30068,7 +30068,7 @@
         <v>1308</v>
       </c>
       <c r="D672" s="9">
-        <v>61308</v>
+        <v>1308</v>
       </c>
       <c r="E672" s="10">
         <v>164000</v>
@@ -30097,7 +30097,7 @@
         <v>1401</v>
       </c>
       <c r="D673" s="9">
-        <v>61401</v>
+        <v>1401</v>
       </c>
       <c r="E673" s="10">
         <v>164000</v>
@@ -30126,7 +30126,7 @@
         <v>1402</v>
       </c>
       <c r="D674" s="9">
-        <v>61402</v>
+        <v>1402</v>
       </c>
       <c r="E674" s="10">
         <v>164000</v>
@@ -30155,7 +30155,7 @@
         <v>1403</v>
       </c>
       <c r="D675" s="9">
-        <v>61403</v>
+        <v>1403</v>
       </c>
       <c r="E675" s="10">
         <v>164000</v>
@@ -30184,7 +30184,7 @@
         <v>1404</v>
       </c>
       <c r="D676" s="9">
-        <v>61404</v>
+        <v>1404</v>
       </c>
       <c r="E676" s="10">
         <v>164000</v>
@@ -30213,7 +30213,7 @@
         <v>1405</v>
       </c>
       <c r="D677" s="9">
-        <v>61405</v>
+        <v>1405</v>
       </c>
       <c r="E677" s="10">
         <v>164000</v>
@@ -30242,7 +30242,7 @@
         <v>1406</v>
       </c>
       <c r="D678" s="9">
-        <v>61406</v>
+        <v>1406</v>
       </c>
       <c r="E678" s="10">
         <v>164000</v>
@@ -30271,7 +30271,7 @@
         <v>1407</v>
       </c>
       <c r="D679" s="9">
-        <v>61407</v>
+        <v>1407</v>
       </c>
       <c r="E679" s="10">
         <v>164000</v>
@@ -30300,7 +30300,7 @@
         <v>1408</v>
       </c>
       <c r="D680" s="9">
-        <v>61408</v>
+        <v>1408</v>
       </c>
       <c r="E680" s="10">
         <v>164000</v>
@@ -30329,7 +30329,7 @@
         <v>1501</v>
       </c>
       <c r="D681" s="9">
-        <v>61501</v>
+        <v>1501</v>
       </c>
       <c r="E681" s="10">
         <v>164000</v>
@@ -30358,7 +30358,7 @@
         <v>1502</v>
       </c>
       <c r="D682" s="9">
-        <v>61502</v>
+        <v>1502</v>
       </c>
       <c r="E682" s="10">
         <v>164000</v>
@@ -30387,7 +30387,7 @@
         <v>1503</v>
       </c>
       <c r="D683" s="9">
-        <v>61503</v>
+        <v>1503</v>
       </c>
       <c r="E683" s="10">
         <v>164000</v>
@@ -30416,7 +30416,7 @@
         <v>1504</v>
       </c>
       <c r="D684" s="9">
-        <v>61504</v>
+        <v>1504</v>
       </c>
       <c r="E684" s="10">
         <v>164000</v>
@@ -30445,7 +30445,7 @@
         <v>1505</v>
       </c>
       <c r="D685" s="9">
-        <v>61505</v>
+        <v>1505</v>
       </c>
       <c r="E685" s="10">
         <v>164000</v>
@@ -30474,7 +30474,7 @@
         <v>1506</v>
       </c>
       <c r="D686" s="9">
-        <v>61506</v>
+        <v>1506</v>
       </c>
       <c r="E686" s="10">
         <v>164000</v>
@@ -30503,7 +30503,7 @@
         <v>1507</v>
       </c>
       <c r="D687" s="9">
-        <v>61507</v>
+        <v>1507</v>
       </c>
       <c r="E687" s="10">
         <v>164000</v>
@@ -30532,7 +30532,7 @@
         <v>1508</v>
       </c>
       <c r="D688" s="9">
-        <v>61508</v>
+        <v>1508</v>
       </c>
       <c r="E688" s="10">
         <v>164000</v>
@@ -30561,7 +30561,7 @@
         <v>102</v>
       </c>
       <c r="D689" s="9">
-        <v>7102</v>
+        <v>102</v>
       </c>
       <c r="E689" s="10">
         <v>153000</v>
@@ -30590,7 +30590,7 @@
         <v>103</v>
       </c>
       <c r="D690" s="9">
-        <v>7103</v>
+        <v>103</v>
       </c>
       <c r="E690" s="10">
         <v>153000</v>
@@ -30619,7 +30619,7 @@
         <v>201</v>
       </c>
       <c r="D691" s="9">
-        <v>7201</v>
+        <v>201</v>
       </c>
       <c r="E691" s="10">
         <v>165000</v>
@@ -30648,7 +30648,7 @@
         <v>202</v>
       </c>
       <c r="D692" s="9">
-        <v>7202</v>
+        <v>202</v>
       </c>
       <c r="E692" s="10">
         <v>165000</v>
@@ -30677,7 +30677,7 @@
         <v>203</v>
       </c>
       <c r="D693" s="9">
-        <v>7203</v>
+        <v>203</v>
       </c>
       <c r="E693" s="10">
         <v>165000</v>
@@ -30706,7 +30706,7 @@
         <v>204</v>
       </c>
       <c r="D694" s="9">
-        <v>7204</v>
+        <v>204</v>
       </c>
       <c r="E694" s="10">
         <v>165000</v>
@@ -30735,7 +30735,7 @@
         <v>301</v>
       </c>
       <c r="D695" s="9">
-        <v>7301</v>
+        <v>301</v>
       </c>
       <c r="E695" s="10">
         <v>165000</v>
@@ -30764,7 +30764,7 @@
         <v>302</v>
       </c>
       <c r="D696" s="9">
-        <v>7302</v>
+        <v>302</v>
       </c>
       <c r="E696" s="10">
         <v>165000</v>
@@ -30793,7 +30793,7 @@
         <v>303</v>
       </c>
       <c r="D697" s="9">
-        <v>7303</v>
+        <v>303</v>
       </c>
       <c r="E697" s="10">
         <v>165000</v>
@@ -30822,7 +30822,7 @@
         <v>304</v>
       </c>
       <c r="D698" s="9">
-        <v>7304</v>
+        <v>304</v>
       </c>
       <c r="E698" s="10">
         <v>165000</v>
@@ -30851,7 +30851,7 @@
         <v>305</v>
       </c>
       <c r="D699" s="9">
-        <v>7305</v>
+        <v>305</v>
       </c>
       <c r="E699" s="10">
         <v>165000</v>
@@ -30880,7 +30880,7 @@
         <v>308</v>
       </c>
       <c r="D700" s="9">
-        <v>7308</v>
+        <v>308</v>
       </c>
       <c r="E700" s="10">
         <v>153000</v>
@@ -30909,7 +30909,7 @@
         <v>401</v>
       </c>
       <c r="D701" s="9">
-        <v>7401</v>
+        <v>401</v>
       </c>
       <c r="E701" s="10">
         <v>165000</v>
@@ -30938,7 +30938,7 @@
         <v>402</v>
       </c>
       <c r="D702" s="9">
-        <v>7402</v>
+        <v>402</v>
       </c>
       <c r="E702" s="10">
         <v>165000</v>
@@ -30967,7 +30967,7 @@
         <v>403</v>
       </c>
       <c r="D703" s="9">
-        <v>7403</v>
+        <v>403</v>
       </c>
       <c r="E703" s="10">
         <v>165000</v>
@@ -30996,7 +30996,7 @@
         <v>404</v>
       </c>
       <c r="D704" s="9">
-        <v>7404</v>
+        <v>404</v>
       </c>
       <c r="E704" s="10">
         <v>165000</v>
@@ -31025,7 +31025,7 @@
         <v>405</v>
       </c>
       <c r="D705" s="9">
-        <v>7405</v>
+        <v>405</v>
       </c>
       <c r="E705" s="10">
         <v>165000</v>
@@ -31054,7 +31054,7 @@
         <v>406</v>
       </c>
       <c r="D706" s="9">
-        <v>7406</v>
+        <v>406</v>
       </c>
       <c r="E706" s="10">
         <v>165000</v>
@@ -31083,7 +31083,7 @@
         <v>407</v>
       </c>
       <c r="D707" s="9">
-        <v>7407</v>
+        <v>407</v>
       </c>
       <c r="E707" s="10">
         <v>165000</v>
@@ -31112,7 +31112,7 @@
         <v>408</v>
       </c>
       <c r="D708" s="9">
-        <v>7408</v>
+        <v>408</v>
       </c>
       <c r="E708" s="10">
         <v>165000</v>
@@ -31141,7 +31141,7 @@
         <v>501</v>
       </c>
       <c r="D709" s="9">
-        <v>7501</v>
+        <v>501</v>
       </c>
       <c r="E709" s="10">
         <v>165000</v>
@@ -31170,7 +31170,7 @@
         <v>502</v>
       </c>
       <c r="D710" s="9">
-        <v>7502</v>
+        <v>502</v>
       </c>
       <c r="E710" s="10">
         <v>165000</v>
@@ -31199,7 +31199,7 @@
         <v>503</v>
       </c>
       <c r="D711" s="9">
-        <v>7503</v>
+        <v>503</v>
       </c>
       <c r="E711" s="10">
         <v>165000</v>
@@ -31228,7 +31228,7 @@
         <v>504</v>
       </c>
       <c r="D712" s="9">
-        <v>7504</v>
+        <v>504</v>
       </c>
       <c r="E712" s="10">
         <v>165000</v>
@@ -31257,7 +31257,7 @@
         <v>505</v>
       </c>
       <c r="D713" s="9">
-        <v>7505</v>
+        <v>505</v>
       </c>
       <c r="E713" s="10">
         <v>165000</v>
@@ -31286,7 +31286,7 @@
         <v>506</v>
       </c>
       <c r="D714" s="9">
-        <v>7506</v>
+        <v>506</v>
       </c>
       <c r="E714" s="10">
         <v>165000</v>
@@ -31315,7 +31315,7 @@
         <v>507</v>
       </c>
       <c r="D715" s="9">
-        <v>7507</v>
+        <v>507</v>
       </c>
       <c r="E715" s="10">
         <v>165000</v>
@@ -31344,7 +31344,7 @@
         <v>508</v>
       </c>
       <c r="D716" s="9">
-        <v>7508</v>
+        <v>508</v>
       </c>
       <c r="E716" s="10">
         <v>165000</v>
@@ -31373,7 +31373,7 @@
         <v>601</v>
       </c>
       <c r="D717" s="9">
-        <v>7601</v>
+        <v>601</v>
       </c>
       <c r="E717" s="10">
         <v>165000</v>
@@ -31402,7 +31402,7 @@
         <v>602</v>
       </c>
       <c r="D718" s="9">
-        <v>7602</v>
+        <v>602</v>
       </c>
       <c r="E718" s="10">
         <v>165000</v>
@@ -31431,7 +31431,7 @@
         <v>603</v>
       </c>
       <c r="D719" s="9">
-        <v>7603</v>
+        <v>603</v>
       </c>
       <c r="E719" s="10">
         <v>165000</v>
@@ -31460,7 +31460,7 @@
         <v>604</v>
       </c>
       <c r="D720" s="9">
-        <v>7604</v>
+        <v>604</v>
       </c>
       <c r="E720" s="10">
         <v>165000</v>
@@ -31489,7 +31489,7 @@
         <v>605</v>
       </c>
       <c r="D721" s="9">
-        <v>7605</v>
+        <v>605</v>
       </c>
       <c r="E721" s="10">
         <v>165000</v>
@@ -31518,7 +31518,7 @@
         <v>606</v>
       </c>
       <c r="D722" s="9">
-        <v>7606</v>
+        <v>606</v>
       </c>
       <c r="E722" s="10">
         <v>165000</v>
@@ -31547,7 +31547,7 @@
         <v>607</v>
       </c>
       <c r="D723" s="9">
-        <v>7607</v>
+        <v>607</v>
       </c>
       <c r="E723" s="10">
         <v>165000</v>
@@ -31576,7 +31576,7 @@
         <v>608</v>
       </c>
       <c r="D724" s="9">
-        <v>7608</v>
+        <v>608</v>
       </c>
       <c r="E724" s="10">
         <v>165000</v>
@@ -31605,7 +31605,7 @@
         <v>701</v>
       </c>
       <c r="D725" s="9">
-        <v>7701</v>
+        <v>701</v>
       </c>
       <c r="E725" s="10">
         <v>165000</v>
@@ -31634,7 +31634,7 @@
         <v>702</v>
       </c>
       <c r="D726" s="9">
-        <v>7702</v>
+        <v>702</v>
       </c>
       <c r="E726" s="10">
         <v>165000</v>
@@ -31663,7 +31663,7 @@
         <v>703</v>
       </c>
       <c r="D727" s="9">
-        <v>7703</v>
+        <v>703</v>
       </c>
       <c r="E727" s="10">
         <v>165000</v>
@@ -31692,7 +31692,7 @@
         <v>704</v>
       </c>
       <c r="D728" s="9">
-        <v>7704</v>
+        <v>704</v>
       </c>
       <c r="E728" s="10">
         <v>165000</v>
@@ -31721,7 +31721,7 @@
         <v>705</v>
       </c>
       <c r="D729" s="9">
-        <v>7705</v>
+        <v>705</v>
       </c>
       <c r="E729" s="10">
         <v>165000</v>
@@ -31750,7 +31750,7 @@
         <v>706</v>
       </c>
       <c r="D730" s="9">
-        <v>7706</v>
+        <v>706</v>
       </c>
       <c r="E730" s="10">
         <v>165000</v>
@@ -31779,7 +31779,7 @@
         <v>707</v>
       </c>
       <c r="D731" s="9">
-        <v>7707</v>
+        <v>707</v>
       </c>
       <c r="E731" s="10">
         <v>165000</v>
@@ -31808,7 +31808,7 @@
         <v>708</v>
       </c>
       <c r="D732" s="9">
-        <v>7708</v>
+        <v>708</v>
       </c>
       <c r="E732" s="10">
         <v>165000</v>
@@ -31837,7 +31837,7 @@
         <v>801</v>
       </c>
       <c r="D733" s="9">
-        <v>7801</v>
+        <v>801</v>
       </c>
       <c r="E733" s="10">
         <v>165000</v>
@@ -31866,7 +31866,7 @@
         <v>802</v>
       </c>
       <c r="D734" s="9">
-        <v>7802</v>
+        <v>802</v>
       </c>
       <c r="E734" s="10">
         <v>165000</v>
@@ -31895,7 +31895,7 @@
         <v>803</v>
       </c>
       <c r="D735" s="9">
-        <v>7803</v>
+        <v>803</v>
       </c>
       <c r="E735" s="10">
         <v>165000</v>
@@ -31924,7 +31924,7 @@
         <v>804</v>
       </c>
       <c r="D736" s="9">
-        <v>7804</v>
+        <v>804</v>
       </c>
       <c r="E736" s="10">
         <v>165000</v>
@@ -31953,7 +31953,7 @@
         <v>805</v>
       </c>
       <c r="D737" s="9">
-        <v>7805</v>
+        <v>805</v>
       </c>
       <c r="E737" s="10">
         <v>165000</v>
@@ -31982,7 +31982,7 @@
         <v>806</v>
       </c>
       <c r="D738" s="9">
-        <v>7806</v>
+        <v>806</v>
       </c>
       <c r="E738" s="10">
         <v>165000</v>
@@ -32011,7 +32011,7 @@
         <v>807</v>
       </c>
       <c r="D739" s="9">
-        <v>7807</v>
+        <v>807</v>
       </c>
       <c r="E739" s="10">
         <v>165000</v>
@@ -32040,7 +32040,7 @@
         <v>808</v>
       </c>
       <c r="D740" s="9">
-        <v>7808</v>
+        <v>808</v>
       </c>
       <c r="E740" s="10">
         <v>165000</v>
@@ -32069,7 +32069,7 @@
         <v>901</v>
       </c>
       <c r="D741" s="9">
-        <v>7901</v>
+        <v>901</v>
       </c>
       <c r="E741" s="10">
         <v>165000</v>
@@ -32098,7 +32098,7 @@
         <v>902</v>
       </c>
       <c r="D742" s="9">
-        <v>7902</v>
+        <v>902</v>
       </c>
       <c r="E742" s="10">
         <v>165000</v>
@@ -32127,7 +32127,7 @@
         <v>903</v>
       </c>
       <c r="D743" s="9">
-        <v>7903</v>
+        <v>903</v>
       </c>
       <c r="E743" s="10">
         <v>165000</v>
@@ -32156,7 +32156,7 @@
         <v>904</v>
       </c>
       <c r="D744" s="9">
-        <v>7904</v>
+        <v>904</v>
       </c>
       <c r="E744" s="10">
         <v>165000</v>
@@ -32185,7 +32185,7 @@
         <v>905</v>
       </c>
       <c r="D745" s="9">
-        <v>7905</v>
+        <v>905</v>
       </c>
       <c r="E745" s="10">
         <v>165000</v>
@@ -32214,7 +32214,7 @@
         <v>906</v>
       </c>
       <c r="D746" s="9">
-        <v>7906</v>
+        <v>906</v>
       </c>
       <c r="E746" s="10">
         <v>165000</v>
@@ -32243,7 +32243,7 @@
         <v>907</v>
       </c>
       <c r="D747" s="9">
-        <v>7907</v>
+        <v>907</v>
       </c>
       <c r="E747" s="10">
         <v>165000</v>
@@ -32272,7 +32272,7 @@
         <v>908</v>
       </c>
       <c r="D748" s="9">
-        <v>7908</v>
+        <v>908</v>
       </c>
       <c r="E748" s="10">
         <v>165000</v>
@@ -32301,7 +32301,7 @@
         <v>1001</v>
       </c>
       <c r="D749" s="9">
-        <v>71001</v>
+        <v>1001</v>
       </c>
       <c r="E749" s="10">
         <v>165000</v>
@@ -32330,7 +32330,7 @@
         <v>1002</v>
       </c>
       <c r="D750" s="9">
-        <v>71002</v>
+        <v>1002</v>
       </c>
       <c r="E750" s="10">
         <v>165000</v>
@@ -32359,7 +32359,7 @@
         <v>1003</v>
       </c>
       <c r="D751" s="9">
-        <v>71003</v>
+        <v>1003</v>
       </c>
       <c r="E751" s="10">
         <v>165000</v>
@@ -32388,7 +32388,7 @@
         <v>1004</v>
       </c>
       <c r="D752" s="9">
-        <v>71004</v>
+        <v>1004</v>
       </c>
       <c r="E752" s="10">
         <v>165000</v>
@@ -32417,7 +32417,7 @@
         <v>1005</v>
       </c>
       <c r="D753" s="9">
-        <v>71005</v>
+        <v>1005</v>
       </c>
       <c r="E753" s="10">
         <v>165000</v>
@@ -32446,7 +32446,7 @@
         <v>1006</v>
       </c>
       <c r="D754" s="9">
-        <v>71006</v>
+        <v>1006</v>
       </c>
       <c r="E754" s="10">
         <v>165000</v>
@@ -32475,7 +32475,7 @@
         <v>1007</v>
       </c>
       <c r="D755" s="9">
-        <v>71007</v>
+        <v>1007</v>
       </c>
       <c r="E755" s="10">
         <v>165000</v>
@@ -32504,7 +32504,7 @@
         <v>1008</v>
       </c>
       <c r="D756" s="9">
-        <v>71008</v>
+        <v>1008</v>
       </c>
       <c r="E756" s="10">
         <v>165000</v>
@@ -32533,7 +32533,7 @@
         <v>1101</v>
       </c>
       <c r="D757" s="9">
-        <v>71101</v>
+        <v>1101</v>
       </c>
       <c r="E757" s="10">
         <v>165000</v>
@@ -32562,7 +32562,7 @@
         <v>1102</v>
       </c>
       <c r="D758" s="9">
-        <v>71102</v>
+        <v>1102</v>
       </c>
       <c r="E758" s="10">
         <v>165000</v>
@@ -32591,7 +32591,7 @@
         <v>1103</v>
       </c>
       <c r="D759" s="9">
-        <v>71103</v>
+        <v>1103</v>
       </c>
       <c r="E759" s="10">
         <v>165000</v>
@@ -32620,7 +32620,7 @@
         <v>1104</v>
       </c>
       <c r="D760" s="9">
-        <v>71104</v>
+        <v>1104</v>
       </c>
       <c r="E760" s="10">
         <v>165000</v>
@@ -32649,7 +32649,7 @@
         <v>1105</v>
       </c>
       <c r="D761" s="9">
-        <v>71105</v>
+        <v>1105</v>
       </c>
       <c r="E761" s="10">
         <v>165000</v>
@@ -32678,7 +32678,7 @@
         <v>1106</v>
       </c>
       <c r="D762" s="9">
-        <v>71106</v>
+        <v>1106</v>
       </c>
       <c r="E762" s="10">
         <v>165000</v>
@@ -32707,7 +32707,7 @@
         <v>1107</v>
       </c>
       <c r="D763" s="9">
-        <v>71107</v>
+        <v>1107</v>
       </c>
       <c r="E763" s="10">
         <v>165000</v>
@@ -32736,7 +32736,7 @@
         <v>1108</v>
       </c>
       <c r="D764" s="9">
-        <v>71108</v>
+        <v>1108</v>
       </c>
       <c r="E764" s="10">
         <v>165000</v>
@@ -32765,7 +32765,7 @@
         <v>1201</v>
       </c>
       <c r="D765" s="9">
-        <v>71201</v>
+        <v>1201</v>
       </c>
       <c r="E765" s="10">
         <v>165000</v>
@@ -32794,7 +32794,7 @@
         <v>1202</v>
       </c>
       <c r="D766" s="9">
-        <v>71202</v>
+        <v>1202</v>
       </c>
       <c r="E766" s="10">
         <v>165000</v>
@@ -32823,7 +32823,7 @@
         <v>1203</v>
       </c>
       <c r="D767" s="9">
-        <v>71203</v>
+        <v>1203</v>
       </c>
       <c r="E767" s="10">
         <v>165000</v>
@@ -32852,7 +32852,7 @@
         <v>1204</v>
       </c>
       <c r="D768" s="9">
-        <v>71204</v>
+        <v>1204</v>
       </c>
       <c r="E768" s="10">
         <v>165000</v>
@@ -32881,7 +32881,7 @@
         <v>1205</v>
       </c>
       <c r="D769" s="9">
-        <v>71205</v>
+        <v>1205</v>
       </c>
       <c r="E769" s="10">
         <v>165000</v>
@@ -32910,7 +32910,7 @@
         <v>1206</v>
       </c>
       <c r="D770" s="9">
-        <v>71206</v>
+        <v>1206</v>
       </c>
       <c r="E770" s="10">
         <v>165000</v>
@@ -32939,7 +32939,7 @@
         <v>1207</v>
       </c>
       <c r="D771" s="9">
-        <v>71207</v>
+        <v>1207</v>
       </c>
       <c r="E771" s="10">
         <v>165000</v>
@@ -32968,7 +32968,7 @@
         <v>1208</v>
       </c>
       <c r="D772" s="9">
-        <v>71208</v>
+        <v>1208</v>
       </c>
       <c r="E772" s="10">
         <v>165000</v>
@@ -32997,7 +32997,7 @@
         <v>1301</v>
       </c>
       <c r="D773" s="9">
-        <v>71301</v>
+        <v>1301</v>
       </c>
       <c r="E773" s="10">
         <v>165000</v>
@@ -33026,7 +33026,7 @@
         <v>1302</v>
       </c>
       <c r="D774" s="9">
-        <v>71302</v>
+        <v>1302</v>
       </c>
       <c r="E774" s="10">
         <v>165000</v>
@@ -33055,7 +33055,7 @@
         <v>1303</v>
       </c>
       <c r="D775" s="9">
-        <v>71303</v>
+        <v>1303</v>
       </c>
       <c r="E775" s="10">
         <v>165000</v>
@@ -33084,7 +33084,7 @@
         <v>1304</v>
       </c>
       <c r="D776" s="9">
-        <v>71304</v>
+        <v>1304</v>
       </c>
       <c r="E776" s="10">
         <v>165000</v>
@@ -33113,7 +33113,7 @@
         <v>1305</v>
       </c>
       <c r="D777" s="9">
-        <v>71305</v>
+        <v>1305</v>
       </c>
       <c r="E777" s="10">
         <v>165000</v>
@@ -33142,7 +33142,7 @@
         <v>1306</v>
       </c>
       <c r="D778" s="9">
-        <v>71306</v>
+        <v>1306</v>
       </c>
       <c r="E778" s="10">
         <v>165000</v>
@@ -33171,7 +33171,7 @@
         <v>1307</v>
       </c>
       <c r="D779" s="9">
-        <v>71307</v>
+        <v>1307</v>
       </c>
       <c r="E779" s="10">
         <v>165000</v>
@@ -33200,7 +33200,7 @@
         <v>1308</v>
       </c>
       <c r="D780" s="9">
-        <v>71308</v>
+        <v>1308</v>
       </c>
       <c r="E780" s="10">
         <v>165000</v>
@@ -33229,7 +33229,7 @@
         <v>1401</v>
       </c>
       <c r="D781" s="9">
-        <v>71401</v>
+        <v>1401</v>
       </c>
       <c r="E781" s="10">
         <v>165000</v>
@@ -33258,7 +33258,7 @@
         <v>1402</v>
       </c>
       <c r="D782" s="9">
-        <v>71402</v>
+        <v>1402</v>
       </c>
       <c r="E782" s="10">
         <v>165000</v>
@@ -33287,7 +33287,7 @@
         <v>1403</v>
       </c>
       <c r="D783" s="9">
-        <v>71403</v>
+        <v>1403</v>
       </c>
       <c r="E783" s="10">
         <v>165000</v>
@@ -33316,7 +33316,7 @@
         <v>1404</v>
       </c>
       <c r="D784" s="9">
-        <v>71404</v>
+        <v>1404</v>
       </c>
       <c r="E784" s="10">
         <v>165000</v>
@@ -33345,7 +33345,7 @@
         <v>1405</v>
       </c>
       <c r="D785" s="9">
-        <v>71405</v>
+        <v>1405</v>
       </c>
       <c r="E785" s="10">
         <v>165000</v>
@@ -33374,7 +33374,7 @@
         <v>1406</v>
       </c>
       <c r="D786" s="9">
-        <v>71406</v>
+        <v>1406</v>
       </c>
       <c r="E786" s="10">
         <v>165000</v>
@@ -33403,7 +33403,7 @@
         <v>1407</v>
       </c>
       <c r="D787" s="9">
-        <v>71407</v>
+        <v>1407</v>
       </c>
       <c r="E787" s="10">
         <v>165000</v>
@@ -33432,7 +33432,7 @@
         <v>1408</v>
       </c>
       <c r="D788" s="9">
-        <v>71408</v>
+        <v>1408</v>
       </c>
       <c r="E788" s="10">
         <v>165000</v>
@@ -33461,7 +33461,7 @@
         <v>1501</v>
       </c>
       <c r="D789" s="9">
-        <v>71501</v>
+        <v>1501</v>
       </c>
       <c r="E789" s="10">
         <v>165000</v>
@@ -33490,7 +33490,7 @@
         <v>1502</v>
       </c>
       <c r="D790" s="9">
-        <v>71502</v>
+        <v>1502</v>
       </c>
       <c r="E790" s="10">
         <v>165000</v>
@@ -33519,7 +33519,7 @@
         <v>1503</v>
       </c>
       <c r="D791" s="9">
-        <v>71503</v>
+        <v>1503</v>
       </c>
       <c r="E791" s="10">
         <v>165000</v>
@@ -33548,7 +33548,7 @@
         <v>1504</v>
       </c>
       <c r="D792" s="9">
-        <v>71504</v>
+        <v>1504</v>
       </c>
       <c r="E792" s="10">
         <v>165000</v>
@@ -33577,7 +33577,7 @@
         <v>1505</v>
       </c>
       <c r="D793" s="9">
-        <v>71505</v>
+        <v>1505</v>
       </c>
       <c r="E793" s="10">
         <v>165000</v>
@@ -33606,7 +33606,7 @@
         <v>1506</v>
       </c>
       <c r="D794" s="9">
-        <v>71506</v>
+        <v>1506</v>
       </c>
       <c r="E794" s="10">
         <v>165000</v>
@@ -33635,7 +33635,7 @@
         <v>1507</v>
       </c>
       <c r="D795" s="9">
-        <v>71507</v>
+        <v>1507</v>
       </c>
       <c r="E795" s="10">
         <v>165000</v>
@@ -33664,7 +33664,7 @@
         <v>1508</v>
       </c>
       <c r="D796" s="9">
-        <v>71508</v>
+        <v>1508</v>
       </c>
       <c r="E796" s="10">
         <v>165000</v>
@@ -33689,7 +33689,9 @@
       <c r="B797" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C797" s="14"/>
+      <c r="C797" s="14">
+        <v>1</v>
+      </c>
       <c r="D797" s="8" t="s">
         <v>11</v>
       </c>
@@ -33716,7 +33718,9 @@
       <c r="B798" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C798" s="14"/>
+      <c r="C798" s="14">
+        <v>2</v>
+      </c>
       <c r="D798" s="8" t="s">
         <v>12</v>
       </c>
@@ -33743,7 +33747,9 @@
       <c r="B799" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C799" s="14"/>
+      <c r="C799" s="14">
+        <v>3</v>
+      </c>
       <c r="D799" s="8" t="s">
         <v>13</v>
       </c>
@@ -33770,7 +33776,9 @@
       <c r="B800" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C800" s="14"/>
+      <c r="C800" s="14">
+        <v>4</v>
+      </c>
       <c r="D800" s="8" t="s">
         <v>14</v>
       </c>

--- a/App_Inmuebles_Automatico/Cuota2026.xlsx
+++ b/App_Inmuebles_Automatico/Cuota2026.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fernando T\Descargas\App_Inmuebles_Automatico\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fernando T\Escritorio\PROGRAMACION\cuotas adm\App_Inmuebles_Automatico\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="11370"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="1" r:id="rId1"/>
@@ -10088,7 +10088,7 @@
     <t>Parqueadero Moto</t>
   </si>
   <si>
-    <t>Cuota Extraordinaria 2026-2</t>
+    <t>2026-2</t>
   </si>
 </sst>
 </file>
